--- a/research/traditional_assets/database/data/turkey/turkey_food_wholesalers.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_food_wholesalers.xlsx
@@ -1397,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1534,22 +1534,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09795920146182607</v>
+        <v>0.0977480534581715</v>
       </c>
       <c r="C2">
-        <v>537.4847654891521</v>
+        <v>534.3166427054842</v>
       </c>
       <c r="D2">
-        <v>537.193765489152</v>
+        <v>539.3772427054842</v>
       </c>
       <c r="E2">
-        <v>-6.76</v>
+        <v>-1.4084</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.351599999999999</v>
       </c>
       <c r="G2">
         <v>0.291</v>
@@ -1570,28 +1570,28 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.26918548</v>
       </c>
       <c r="N2">
-        <v>17.78888888888889</v>
+        <v>17.51970340888889</v>
       </c>
       <c r="O2">
-        <v>4.447222222222223</v>
+        <v>4.379925852222223</v>
       </c>
       <c r="P2">
-        <v>13.34166666666667</v>
+        <v>13.13977755666667</v>
       </c>
       <c r="Q2">
-        <v>14.44166666666667</v>
+        <v>14.23977755666667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09795920146182607</v>
+        <v>0.09835434692744596</v>
       </c>
       <c r="T2">
-        <v>0.5044193424952811</v>
+        <v>0.5082407011505483</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>66.08413235694917</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1616,22 +1616,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0977480534581715</v>
+        <v>0.09753690545451696</v>
       </c>
       <c r="C3">
-        <v>534.3166427054842</v>
+        <v>531.1663422809695</v>
       </c>
       <c r="D3">
-        <v>539.3772427054842</v>
+        <v>541.5785422809695</v>
       </c>
       <c r="E3">
-        <v>-1.4084</v>
+        <v>3.943199999999999</v>
       </c>
       <c r="F3">
-        <v>5.351599999999999</v>
+        <v>10.7032</v>
       </c>
       <c r="G3">
         <v>0.291</v>
@@ -1652,28 +1652,28 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M3">
-        <v>0.26918548</v>
+        <v>0.53837096</v>
       </c>
       <c r="N3">
-        <v>17.51970340888889</v>
+        <v>17.25051792888889</v>
       </c>
       <c r="O3">
-        <v>4.379925852222223</v>
+        <v>4.312629482222222</v>
       </c>
       <c r="P3">
-        <v>13.13977755666667</v>
+        <v>12.93788844666667</v>
       </c>
       <c r="Q3">
-        <v>14.23977755666667</v>
+        <v>14.03788844666667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09835434692744596</v>
+        <v>0.09875755658624179</v>
       </c>
       <c r="T3">
-        <v>0.5082407011505483</v>
+        <v>0.5121400467171476</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>66.08413235694917</v>
+        <v>33.04206617847458</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1698,22 +1698,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09753690545451696</v>
+        <v>0.09732575745086237</v>
       </c>
       <c r="C4">
-        <v>531.1663422809695</v>
+        <v>528.0340833189706</v>
       </c>
       <c r="D4">
-        <v>541.5785422809695</v>
+        <v>543.7978833189705</v>
       </c>
       <c r="E4">
-        <v>3.943199999999999</v>
+        <v>9.2948</v>
       </c>
       <c r="F4">
-        <v>10.7032</v>
+        <v>16.0548</v>
       </c>
       <c r="G4">
         <v>0.291</v>
@@ -1734,28 +1734,28 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M4">
-        <v>0.53837096</v>
+        <v>0.8075564399999999</v>
       </c>
       <c r="N4">
-        <v>17.25051792888889</v>
+        <v>16.98133244888889</v>
       </c>
       <c r="O4">
-        <v>4.312629482222222</v>
+        <v>4.245333112222223</v>
       </c>
       <c r="P4">
-        <v>12.93788844666667</v>
+        <v>12.73599933666667</v>
       </c>
       <c r="Q4">
-        <v>14.03788844666667</v>
+        <v>13.83599933666667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09875755658624179</v>
+        <v>0.09916907984624987</v>
       </c>
       <c r="T4">
-        <v>0.5121400467171476</v>
+        <v>0.5161197911614087</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>33.04206617847458</v>
+        <v>22.02804411898306</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1780,22 +1780,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09732575745086237</v>
+        <v>0.09711460944720782</v>
       </c>
       <c r="C5">
-        <v>528.0340833189706</v>
+        <v>524.9200885290911</v>
       </c>
       <c r="D5">
-        <v>543.7978833189705</v>
+        <v>546.035488529091</v>
       </c>
       <c r="E5">
-        <v>9.2948</v>
+        <v>14.6464</v>
       </c>
       <c r="F5">
-        <v>16.0548</v>
+        <v>21.4064</v>
       </c>
       <c r="G5">
         <v>0.291</v>
@@ -1816,28 +1816,28 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M5">
-        <v>0.8075564399999999</v>
+        <v>1.07674192</v>
       </c>
       <c r="N5">
-        <v>16.98133244888889</v>
+        <v>16.71214696888889</v>
       </c>
       <c r="O5">
-        <v>4.245333112222223</v>
+        <v>4.178036742222223</v>
       </c>
       <c r="P5">
-        <v>12.73599933666667</v>
+        <v>12.53411022666667</v>
       </c>
       <c r="Q5">
-        <v>13.83599933666667</v>
+        <v>13.63411022666667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09916907984624987</v>
+        <v>0.09958917650750815</v>
       </c>
       <c r="T5">
-        <v>0.5161197911614087</v>
+        <v>0.5201824469482587</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>22.02804411898306</v>
+        <v>16.52103308923729</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1862,22 +1862,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09711460944720782</v>
+        <v>0.09690346144355326</v>
       </c>
       <c r="C6">
-        <v>524.9200885290911</v>
+        <v>521.82458430168</v>
       </c>
       <c r="D6">
-        <v>546.035488529091</v>
+        <v>548.29158430168</v>
       </c>
       <c r="E6">
-        <v>14.6464</v>
+        <v>19.998</v>
       </c>
       <c r="F6">
-        <v>21.4064</v>
+        <v>26.758</v>
       </c>
       <c r="G6">
         <v>0.291</v>
@@ -1898,28 +1898,28 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M6">
-        <v>1.07674192</v>
+        <v>1.3459274</v>
       </c>
       <c r="N6">
-        <v>16.71214696888889</v>
+        <v>16.44296148888889</v>
       </c>
       <c r="O6">
-        <v>4.178036742222223</v>
+        <v>4.110740372222223</v>
       </c>
       <c r="P6">
-        <v>12.53411022666667</v>
+        <v>12.33222111666667</v>
       </c>
       <c r="Q6">
-        <v>13.63411022666667</v>
+        <v>13.43222111666667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09958917650750815</v>
+        <v>0.1000181173090034</v>
       </c>
       <c r="T6">
-        <v>0.5201824469482587</v>
+        <v>0.5243306323306212</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>16.52103308923729</v>
+        <v>13.21682647138983</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1944,22 +1944,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09690346144355326</v>
+        <v>0.09675981343989867</v>
       </c>
       <c r="C7">
-        <v>521.82458430168</v>
+        <v>518.0185353190211</v>
       </c>
       <c r="D7">
-        <v>548.29158430168</v>
+        <v>549.8371353190211</v>
       </c>
       <c r="E7">
-        <v>19.998</v>
+        <v>25.3496</v>
       </c>
       <c r="F7">
-        <v>26.758</v>
+        <v>32.1096</v>
       </c>
       <c r="G7">
         <v>0.291</v>
@@ -1980,45 +1980,45 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M7">
-        <v>1.3459274</v>
+        <v>1.66327728</v>
       </c>
       <c r="N7">
-        <v>16.44296148888889</v>
+        <v>16.12561160888889</v>
       </c>
       <c r="O7">
-        <v>4.110740372222223</v>
+        <v>4.031402902222223</v>
       </c>
       <c r="P7">
-        <v>12.33222111666667</v>
+        <v>12.09420870666667</v>
       </c>
       <c r="Q7">
-        <v>13.43222111666667</v>
+        <v>13.19420870666667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1000181173090034</v>
+        <v>0.1004561845105305</v>
       </c>
       <c r="T7">
-        <v>0.5243306323306212</v>
+        <v>0.5285670769764381</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>13.21682647138983</v>
+        <v>10.69508319676494</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2026,22 +2026,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09675981343989867</v>
+        <v>0.09664916543624412</v>
       </c>
       <c r="C8">
-        <v>518.0185353190211</v>
+        <v>513.8633833007382</v>
       </c>
       <c r="D8">
-        <v>549.8371353190211</v>
+        <v>551.0335833007381</v>
       </c>
       <c r="E8">
-        <v>25.3496</v>
+        <v>30.70119999999999</v>
       </c>
       <c r="F8">
-        <v>32.1096</v>
+        <v>37.46119999999999</v>
       </c>
       <c r="G8">
         <v>0.291</v>
@@ -2062,45 +2062,45 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M8">
-        <v>1.66327728</v>
+        <v>2.0041742</v>
       </c>
       <c r="N8">
-        <v>16.12561160888889</v>
+        <v>15.78471468888889</v>
       </c>
       <c r="O8">
-        <v>4.031402902222223</v>
+        <v>3.946178672222223</v>
       </c>
       <c r="P8">
-        <v>12.09420870666667</v>
+        <v>11.83853601666667</v>
       </c>
       <c r="Q8">
-        <v>13.19420870666667</v>
+        <v>12.93853601666667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1004561845105305</v>
+        <v>0.1009036725120905</v>
       </c>
       <c r="T8">
-        <v>0.5285670769764381</v>
+        <v>0.5328946279587243</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>10.69508319676494</v>
+        <v>8.875919512829221</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2108,22 +2108,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09664916543624412</v>
+        <v>0.09646201743258956</v>
       </c>
       <c r="C9">
-        <v>513.8633833007382</v>
+        <v>510.547328671559</v>
       </c>
       <c r="D9">
-        <v>551.0335833007381</v>
+        <v>553.0691286715589</v>
       </c>
       <c r="E9">
-        <v>30.7012</v>
+        <v>36.0528</v>
       </c>
       <c r="F9">
-        <v>37.4612</v>
+        <v>42.8128</v>
       </c>
       <c r="G9">
         <v>0.291</v>
@@ -2144,28 +2144,28 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M9">
-        <v>2.0041742</v>
+        <v>2.2904848</v>
       </c>
       <c r="N9">
-        <v>15.78471468888889</v>
+        <v>15.49840408888889</v>
       </c>
       <c r="O9">
-        <v>3.946178672222223</v>
+        <v>3.874601022222223</v>
       </c>
       <c r="P9">
-        <v>11.83853601666667</v>
+        <v>11.62380306666667</v>
       </c>
       <c r="Q9">
-        <v>12.93853601666667</v>
+        <v>12.72380306666667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1009036725120905</v>
+        <v>0.1013608885136843</v>
       </c>
       <c r="T9">
-        <v>0.5328946279587243</v>
+        <v>0.5373162561362778</v>
       </c>
       <c r="U9">
         <v>0.0535</v>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>8.875919512829221</v>
+        <v>7.766429573725568</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2190,22 +2190,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09646201743258956</v>
+        <v>0.096328869428935</v>
       </c>
       <c r="C10">
-        <v>510.547328671559</v>
+        <v>506.6531143443011</v>
       </c>
       <c r="D10">
-        <v>553.0691286715589</v>
+        <v>554.5265143443011</v>
       </c>
       <c r="E10">
-        <v>36.0528</v>
+        <v>41.4044</v>
       </c>
       <c r="F10">
-        <v>42.8128</v>
+        <v>48.16439999999999</v>
       </c>
       <c r="G10">
         <v>0.291</v>
@@ -2226,45 +2226,45 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M10">
-        <v>2.2904848</v>
+        <v>2.61532692</v>
       </c>
       <c r="N10">
-        <v>15.49840408888889</v>
+        <v>15.17356196888889</v>
       </c>
       <c r="O10">
-        <v>3.874601022222223</v>
+        <v>3.793390492222223</v>
       </c>
       <c r="P10">
-        <v>11.62380306666667</v>
+        <v>11.38017147666667</v>
       </c>
       <c r="Q10">
-        <v>12.72380306666667</v>
+        <v>12.48017147666667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1013608885136843</v>
+        <v>0.1018281532186099</v>
       </c>
       <c r="T10">
-        <v>0.5373162561362778</v>
+        <v>0.5418350629550959</v>
       </c>
       <c r="U10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y10">
-        <v>7.766429573725568</v>
+        <v>6.801784034283902</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2272,22 +2272,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.096328869428935</v>
+        <v>0.09614772142528041</v>
       </c>
       <c r="C11">
-        <v>506.6531143443011</v>
+        <v>503.2966666213725</v>
       </c>
       <c r="D11">
-        <v>554.5265143443011</v>
+        <v>556.5216666213724</v>
       </c>
       <c r="E11">
-        <v>41.4044</v>
+        <v>46.75599999999999</v>
       </c>
       <c r="F11">
-        <v>48.16439999999999</v>
+        <v>53.51599999999999</v>
       </c>
       <c r="G11">
         <v>0.291</v>
@@ -2308,28 +2308,28 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M11">
-        <v>2.61532692</v>
+        <v>2.905918799999999</v>
       </c>
       <c r="N11">
-        <v>15.17356196888889</v>
+        <v>14.88297008888889</v>
       </c>
       <c r="O11">
-        <v>3.793390492222223</v>
+        <v>3.720742522222223</v>
       </c>
       <c r="P11">
-        <v>11.38017147666667</v>
+        <v>11.16222756666667</v>
       </c>
       <c r="Q11">
-        <v>12.48017147666667</v>
+        <v>12.26222756666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1018281532186099</v>
+        <v>0.1023058015836449</v>
       </c>
       <c r="T11">
-        <v>0.5418350629550959</v>
+        <v>0.5464542877032211</v>
       </c>
       <c r="U11">
         <v>0.0543</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>6.801784034283902</v>
+        <v>6.121605630855513</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09614772142528041</v>
+        <v>0.09604907342162587</v>
       </c>
       <c r="C12">
-        <v>503.2966666213725</v>
+        <v>499.037619133576</v>
       </c>
       <c r="D12">
-        <v>556.5216666213724</v>
+        <v>557.6142191335759</v>
       </c>
       <c r="E12">
-        <v>46.756</v>
+        <v>52.1076</v>
       </c>
       <c r="F12">
-        <v>53.516</v>
+        <v>58.8676</v>
       </c>
       <c r="G12">
         <v>0.291</v>
@@ -2390,45 +2390,45 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M12">
-        <v>2.9059188</v>
+        <v>3.25537828</v>
       </c>
       <c r="N12">
-        <v>14.88297008888889</v>
+        <v>14.53351060888889</v>
       </c>
       <c r="O12">
-        <v>3.720742522222223</v>
+        <v>3.633377652222223</v>
       </c>
       <c r="P12">
-        <v>11.16222756666667</v>
+        <v>10.90013295666667</v>
       </c>
       <c r="Q12">
-        <v>12.26222756666667</v>
+        <v>12.00013295666667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1023058015836449</v>
+        <v>0.1027941836198043</v>
       </c>
       <c r="T12">
-        <v>0.5464542877032211</v>
+        <v>0.5511773152546752</v>
       </c>
       <c r="U12">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>6.121605630855512</v>
+        <v>5.464461380165285</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2436,22 +2436,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09604907342162587</v>
+        <v>0.09587542541797128</v>
       </c>
       <c r="C13">
-        <v>499.037619133576</v>
+        <v>495.6196741181067</v>
       </c>
       <c r="D13">
-        <v>557.6142191335759</v>
+        <v>559.5478741181066</v>
       </c>
       <c r="E13">
-        <v>52.1076</v>
+        <v>57.4592</v>
       </c>
       <c r="F13">
-        <v>58.8676</v>
+        <v>64.2192</v>
       </c>
       <c r="G13">
         <v>0.291</v>
@@ -2472,28 +2472,28 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M13">
-        <v>3.25537828</v>
+        <v>3.55132176</v>
       </c>
       <c r="N13">
-        <v>14.53351060888889</v>
+        <v>14.23756712888889</v>
       </c>
       <c r="O13">
-        <v>3.633377652222223</v>
+        <v>3.559391782222223</v>
       </c>
       <c r="P13">
-        <v>10.90013295666667</v>
+        <v>10.67817534666667</v>
       </c>
       <c r="Q13">
-        <v>12.00013295666667</v>
+        <v>11.77817534666667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1027941836198043</v>
+        <v>0.1032936652476946</v>
       </c>
       <c r="T13">
-        <v>0.5511773152546752</v>
+        <v>0.5560076843413894</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.464461380165285</v>
+        <v>5.009089598484844</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2518,22 +2518,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09587542541797128</v>
+        <v>0.09570177741431674</v>
       </c>
       <c r="C14">
-        <v>495.6196741181067</v>
+        <v>492.2151865522598</v>
       </c>
       <c r="D14">
-        <v>559.5478741181066</v>
+        <v>561.4949865522597</v>
       </c>
       <c r="E14">
-        <v>57.4592</v>
+        <v>62.81079999999999</v>
       </c>
       <c r="F14">
-        <v>64.2192</v>
+        <v>69.57079999999999</v>
       </c>
       <c r="G14">
         <v>0.291</v>
@@ -2554,28 +2554,28 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M14">
-        <v>3.55132176</v>
+        <v>3.84726524</v>
       </c>
       <c r="N14">
-        <v>14.23756712888889</v>
+        <v>13.94162364888889</v>
       </c>
       <c r="O14">
-        <v>3.559391782222223</v>
+        <v>3.485405912222223</v>
       </c>
       <c r="P14">
-        <v>10.67817534666667</v>
+        <v>10.45621773666667</v>
       </c>
       <c r="Q14">
-        <v>11.77817534666667</v>
+        <v>11.55621773666667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1032936652476946</v>
+        <v>0.1038046292118583</v>
       </c>
       <c r="T14">
-        <v>0.5560076843413894</v>
+        <v>0.5609490963956143</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.009089598484844</v>
+        <v>4.623775013986011</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2600,22 +2600,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09570177741431674</v>
+        <v>0.09579062941066216</v>
       </c>
       <c r="C15">
-        <v>492.2151865522598</v>
+        <v>485.8656005080498</v>
       </c>
       <c r="D15">
-        <v>561.4949865522597</v>
+        <v>560.4970005080497</v>
       </c>
       <c r="E15">
-        <v>62.81079999999999</v>
+        <v>68.16239999999999</v>
       </c>
       <c r="F15">
-        <v>69.57079999999999</v>
+        <v>74.9224</v>
       </c>
       <c r="G15">
         <v>0.291</v>
@@ -2636,45 +2636,45 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M15">
-        <v>3.84726524</v>
+        <v>4.33051472</v>
       </c>
       <c r="N15">
-        <v>13.94162364888889</v>
+        <v>13.45837416888889</v>
       </c>
       <c r="O15">
-        <v>3.485405912222223</v>
+        <v>3.364593542222223</v>
       </c>
       <c r="P15">
-        <v>10.45621773666667</v>
+        <v>10.09378062666667</v>
       </c>
       <c r="Q15">
-        <v>11.55621773666667</v>
+        <v>11.19378062666667</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1038046292118583</v>
+        <v>0.1043274760589095</v>
       </c>
       <c r="T15">
-        <v>0.5609490963956143</v>
+        <v>0.5660054250092398</v>
       </c>
       <c r="U15">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.623775013986011</v>
+        <v>4.107800120556776</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2682,22 +2682,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09579062941066216</v>
+        <v>0.09602948140700761</v>
       </c>
       <c r="C16">
-        <v>485.8656005080498</v>
+        <v>477.8487166196459</v>
       </c>
       <c r="D16">
-        <v>560.4970005080497</v>
+        <v>557.8317166196458</v>
       </c>
       <c r="E16">
-        <v>68.16239999999999</v>
+        <v>73.514</v>
       </c>
       <c r="F16">
-        <v>74.9224</v>
+        <v>80.274</v>
       </c>
       <c r="G16">
         <v>0.291</v>
@@ -2718,45 +2718,45 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M16">
-        <v>4.33051472</v>
+        <v>4.9207962</v>
       </c>
       <c r="N16">
-        <v>13.45837416888889</v>
+        <v>12.86809268888889</v>
       </c>
       <c r="O16">
-        <v>3.364593542222223</v>
+        <v>3.217023172222223</v>
       </c>
       <c r="P16">
-        <v>10.09378062666667</v>
+        <v>9.651069516666668</v>
       </c>
       <c r="Q16">
-        <v>11.19378062666667</v>
+        <v>10.75106951666667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1043274760589095</v>
+        <v>0.1048626251847148</v>
       </c>
       <c r="T16">
-        <v>0.5660054250092398</v>
+        <v>0.571180726060833</v>
       </c>
       <c r="U16">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.107800120556776</v>
+        <v>3.615042803213206</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2764,22 +2764,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09602948140700761</v>
+        <v>0.09623683340335304</v>
       </c>
       <c r="C17">
-        <v>477.8487166196459</v>
+        <v>470.2038021456608</v>
       </c>
       <c r="D17">
-        <v>557.8317166196458</v>
+        <v>555.5384021456607</v>
       </c>
       <c r="E17">
-        <v>73.51399999999998</v>
+        <v>78.86559999999999</v>
       </c>
       <c r="F17">
-        <v>80.27399999999999</v>
+        <v>85.62559999999999</v>
       </c>
       <c r="G17">
         <v>0.291</v>
@@ -2800,45 +2800,45 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M17">
-        <v>4.920796199999999</v>
+        <v>5.488600959999999</v>
       </c>
       <c r="N17">
-        <v>12.86809268888889</v>
+        <v>12.30028792888889</v>
       </c>
       <c r="O17">
-        <v>3.217023172222223</v>
+        <v>3.075071982222223</v>
       </c>
       <c r="P17">
-        <v>9.65106951666667</v>
+        <v>9.225215946666669</v>
       </c>
       <c r="Q17">
-        <v>10.75106951666667</v>
+        <v>10.32521594666667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1048626251847148</v>
+        <v>0.1054105159563727</v>
       </c>
       <c r="T17">
-        <v>0.571180726060833</v>
+        <v>0.5764792485660355</v>
       </c>
       <c r="U17">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y17">
-        <v>3.615042803213207</v>
+        <v>3.241060703543821</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2846,22 +2846,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09623683340335304</v>
+        <v>0.09612918539969847</v>
       </c>
       <c r="C18">
-        <v>470.2038021456608</v>
+        <v>466.0404311914817</v>
       </c>
       <c r="D18">
-        <v>555.5384021456607</v>
+        <v>556.7266311914816</v>
       </c>
       <c r="E18">
-        <v>78.86559999999999</v>
+        <v>84.21719999999999</v>
       </c>
       <c r="F18">
-        <v>85.62559999999999</v>
+        <v>90.9772</v>
       </c>
       <c r="G18">
         <v>0.291</v>
@@ -2882,28 +2882,28 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M18">
-        <v>5.488600959999999</v>
+        <v>5.83163852</v>
       </c>
       <c r="N18">
-        <v>12.30028792888889</v>
+        <v>11.95725036888889</v>
       </c>
       <c r="O18">
-        <v>3.075071982222223</v>
+        <v>2.989312592222223</v>
       </c>
       <c r="P18">
-        <v>9.225215946666669</v>
+        <v>8.967937776666668</v>
       </c>
       <c r="Q18">
-        <v>10.32521594666667</v>
+        <v>10.06793777666667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1054105159563727</v>
+        <v>0.1059716089152994</v>
       </c>
       <c r="T18">
-        <v>0.5764792485660355</v>
+        <v>0.5819054463123273</v>
       </c>
       <c r="U18">
         <v>0.0641</v>
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.241060703543821</v>
+        <v>3.050410073923596</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2928,22 +2928,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09612918539969847</v>
+        <v>0.09707453739604389</v>
       </c>
       <c r="C19">
-        <v>466.0404311914817</v>
+        <v>450.4244259146408</v>
       </c>
       <c r="D19">
-        <v>556.7266311914816</v>
+        <v>546.4622259146407</v>
       </c>
       <c r="E19">
-        <v>84.21719999999999</v>
+        <v>89.5688</v>
       </c>
       <c r="F19">
-        <v>90.9772</v>
+        <v>96.3288</v>
       </c>
       <c r="G19">
         <v>0.291</v>
@@ -2964,45 +2964,45 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M19">
-        <v>5.83163852</v>
+        <v>6.92604072</v>
       </c>
       <c r="N19">
-        <v>11.95725036888889</v>
+        <v>10.86284816888889</v>
       </c>
       <c r="O19">
-        <v>2.989312592222223</v>
+        <v>2.715712042222223</v>
       </c>
       <c r="P19">
-        <v>8.967937776666668</v>
+        <v>8.14713612666667</v>
       </c>
       <c r="Q19">
-        <v>10.06793777666667</v>
+        <v>9.247136126666669</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1059716089152994</v>
+        <v>0.1065463870683462</v>
       </c>
       <c r="T19">
-        <v>0.5819054463123273</v>
+        <v>0.5874639903451139</v>
       </c>
       <c r="U19">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>3.050410073923596</v>
+        <v>2.568406627688566</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3010,22 +3010,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09707453739604391</v>
+        <v>0.09758113939238937</v>
       </c>
       <c r="C20">
-        <v>450.4244259146407</v>
+        <v>439.7264998618689</v>
       </c>
       <c r="D20">
-        <v>546.4622259146406</v>
+        <v>541.1158998618688</v>
       </c>
       <c r="E20">
-        <v>89.56879999999998</v>
+        <v>94.92039999999999</v>
       </c>
       <c r="F20">
-        <v>96.32879999999999</v>
+        <v>101.6804</v>
       </c>
       <c r="G20">
         <v>0.291</v>
@@ -3046,45 +3046,45 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M20">
-        <v>6.92604072</v>
+        <v>7.70737432</v>
       </c>
       <c r="N20">
-        <v>10.86284816888889</v>
+        <v>10.08151456888889</v>
       </c>
       <c r="O20">
-        <v>2.715712042222223</v>
+        <v>2.520378642222223</v>
       </c>
       <c r="P20">
-        <v>8.14713612666667</v>
+        <v>7.561135926666669</v>
       </c>
       <c r="Q20">
-        <v>9.247136126666669</v>
+        <v>8.661135926666669</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1065463870683462</v>
+        <v>0.1071353572745548</v>
       </c>
       <c r="T20">
-        <v>0.5874639903451139</v>
+        <v>0.5931597823787103</v>
       </c>
       <c r="U20">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y20">
-        <v>2.568406627688566</v>
+        <v>2.308034896232845</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3092,22 +3092,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09758113939238937</v>
+        <v>0.09756124138873479</v>
       </c>
       <c r="C21">
-        <v>439.7264998618689</v>
+        <v>434.582915084536</v>
       </c>
       <c r="D21">
-        <v>541.1158998618688</v>
+        <v>541.3239150845359</v>
       </c>
       <c r="E21">
-        <v>94.92039999999999</v>
+        <v>100.272</v>
       </c>
       <c r="F21">
-        <v>101.6804</v>
+        <v>107.032</v>
       </c>
       <c r="G21">
         <v>0.291</v>
@@ -3128,28 +3128,28 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M21">
-        <v>7.70737432</v>
+        <v>8.1130256</v>
       </c>
       <c r="N21">
-        <v>10.08151456888889</v>
+        <v>9.675863288888891</v>
       </c>
       <c r="O21">
-        <v>2.520378642222223</v>
+        <v>2.418965822222223</v>
       </c>
       <c r="P21">
-        <v>7.561135926666669</v>
+        <v>7.256897466666668</v>
       </c>
       <c r="Q21">
-        <v>8.661135926666669</v>
+        <v>8.356897466666668</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1071353572745548</v>
+        <v>0.1077390517359185</v>
       </c>
       <c r="T21">
-        <v>0.5931597823787103</v>
+        <v>0.5989979692131463</v>
       </c>
       <c r="U21">
         <v>0.07580000000000001</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.308034896232845</v>
+        <v>2.192633151421203</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3174,22 +3174,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09756124138873479</v>
+        <v>0.09754134338508021</v>
       </c>
       <c r="C22">
-        <v>434.582915084536</v>
+        <v>429.4394902987066</v>
       </c>
       <c r="D22">
-        <v>541.3239150845359</v>
+        <v>541.5320902987065</v>
       </c>
       <c r="E22">
-        <v>100.272</v>
+        <v>105.6236</v>
       </c>
       <c r="F22">
-        <v>107.032</v>
+        <v>112.3836</v>
       </c>
       <c r="G22">
         <v>0.291</v>
@@ -3210,28 +3210,28 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M22">
-        <v>8.1130256</v>
+        <v>8.518676880000001</v>
       </c>
       <c r="N22">
-        <v>9.675863288888891</v>
+        <v>9.27021200888889</v>
       </c>
       <c r="O22">
-        <v>2.418965822222223</v>
+        <v>2.317553002222223</v>
       </c>
       <c r="P22">
-        <v>7.256897466666668</v>
+        <v>6.952659006666668</v>
       </c>
       <c r="Q22">
-        <v>8.356897466666668</v>
+        <v>8.052659006666667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1077390517359185</v>
+        <v>0.1083580296013673</v>
       </c>
       <c r="T22">
-        <v>0.5989979692131463</v>
+        <v>0.6049839582459225</v>
       </c>
       <c r="U22">
         <v>0.07580000000000001</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.192633151421203</v>
+        <v>2.088222048972574</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3256,22 +3256,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09754134338508021</v>
+        <v>0.09986444538142564</v>
       </c>
       <c r="C23">
-        <v>429.4394902987066</v>
+        <v>400.8187293708069</v>
       </c>
       <c r="D23">
-        <v>541.5320902987065</v>
+        <v>518.2629293708068</v>
       </c>
       <c r="E23">
-        <v>105.6236</v>
+        <v>110.9752</v>
       </c>
       <c r="F23">
-        <v>112.3836</v>
+        <v>117.7352</v>
       </c>
       <c r="G23">
         <v>0.291</v>
@@ -3292,45 +3292,45 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M23">
-        <v>8.518676879999999</v>
+        <v>10.596168</v>
       </c>
       <c r="N23">
-        <v>9.270212008888892</v>
+        <v>7.192720888888893</v>
       </c>
       <c r="O23">
-        <v>2.317553002222223</v>
+        <v>1.798180222222223</v>
       </c>
       <c r="P23">
-        <v>6.95265900666667</v>
+        <v>5.39454066666667</v>
       </c>
       <c r="Q23">
-        <v>8.052659006666669</v>
+        <v>6.494540666666669</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1083580296013673</v>
+        <v>0.1089928786941354</v>
       </c>
       <c r="T23">
-        <v>0.6049839582459225</v>
+        <v>0.6111234341769751</v>
       </c>
       <c r="U23">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>2.088222048972574</v>
+        <v>1.678803968461891</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3338,22 +3338,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09986444538142564</v>
+        <v>0.09995104737777108</v>
       </c>
       <c r="C24">
-        <v>400.8187293708069</v>
+        <v>394.6382884436455</v>
       </c>
       <c r="D24">
-        <v>518.2629293708068</v>
+        <v>517.4340884436455</v>
       </c>
       <c r="E24">
-        <v>110.9752</v>
+        <v>116.3268</v>
       </c>
       <c r="F24">
-        <v>117.7352</v>
+        <v>123.0868</v>
       </c>
       <c r="G24">
         <v>0.291</v>
@@ -3374,28 +3374,28 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M24">
-        <v>10.596168</v>
+        <v>11.077812</v>
       </c>
       <c r="N24">
-        <v>7.192720888888893</v>
+        <v>6.711076888888892</v>
       </c>
       <c r="O24">
-        <v>1.798180222222223</v>
+        <v>1.677769222222223</v>
       </c>
       <c r="P24">
-        <v>5.39454066666667</v>
+        <v>5.033307666666669</v>
       </c>
       <c r="Q24">
-        <v>6.494540666666669</v>
+        <v>6.133307666666669</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1089928786941354</v>
+        <v>0.1096442173737287</v>
       </c>
       <c r="T24">
-        <v>0.6111234341769751</v>
+        <v>0.6174223770153279</v>
       </c>
       <c r="U24">
         <v>0.09</v>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>1.678803968461891</v>
+        <v>1.605812491572243</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3420,22 +3420,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09995104737777108</v>
+        <v>0.1000376493741165</v>
       </c>
       <c r="C25">
-        <v>394.6382884436455</v>
+        <v>388.4604943597664</v>
       </c>
       <c r="D25">
-        <v>517.4340884436455</v>
+        <v>516.6078943597663</v>
       </c>
       <c r="E25">
-        <v>116.3268</v>
+        <v>121.6784</v>
       </c>
       <c r="F25">
-        <v>123.0868</v>
+        <v>128.4384</v>
       </c>
       <c r="G25">
         <v>0.291</v>
@@ -3456,28 +3456,28 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M25">
-        <v>11.077812</v>
+        <v>11.559456</v>
       </c>
       <c r="N25">
-        <v>6.711076888888892</v>
+        <v>6.229432888888892</v>
       </c>
       <c r="O25">
-        <v>1.677769222222223</v>
+        <v>1.557358222222223</v>
       </c>
       <c r="P25">
-        <v>5.033307666666669</v>
+        <v>4.672074666666669</v>
       </c>
       <c r="Q25">
-        <v>6.133307666666669</v>
+        <v>5.772074666666668</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1096442173737287</v>
+        <v>0.1103126965448901</v>
       </c>
       <c r="T25">
-        <v>0.6174223770153279</v>
+        <v>0.6238870815073214</v>
       </c>
       <c r="U25">
         <v>0.09</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>1.605812491572243</v>
+        <v>1.538903637756733</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3502,22 +3502,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1000376493741165</v>
+        <v>0.1119464847722361</v>
       </c>
       <c r="C26">
-        <v>388.4604943597664</v>
+        <v>290.1001970649118</v>
       </c>
       <c r="D26">
-        <v>516.6078943597663</v>
+        <v>423.5991970649118</v>
       </c>
       <c r="E26">
-        <v>121.6784</v>
+        <v>127.03</v>
       </c>
       <c r="F26">
-        <v>128.4384</v>
+        <v>133.79</v>
       </c>
       <c r="G26">
         <v>0.291</v>
@@ -3538,45 +3538,45 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M26">
-        <v>11.559456</v>
+        <v>19.640372</v>
       </c>
       <c r="N26">
-        <v>6.229432888888892</v>
+        <v>-1.851483111111108</v>
       </c>
       <c r="O26">
-        <v>1.557358222222223</v>
+        <v>-0.462870777777777</v>
       </c>
       <c r="P26">
-        <v>4.672074666666669</v>
+        <v>-1.388612333333331</v>
       </c>
       <c r="Q26">
-        <v>5.772074666666668</v>
+        <v>-0.2886123333333313</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1103126965448901</v>
+        <v>0.11140875255483</v>
       </c>
       <c r="T26">
-        <v>0.6238870815073214</v>
+        <v>0.6344867808197518</v>
       </c>
       <c r="U26">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V26">
-        <v>0.25</v>
+        <v>0.2264326878443149</v>
       </c>
       <c r="W26">
-        <v>0.0675</v>
+        <v>0.1135596814244546</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y26">
-        <v>1.538903637756733</v>
+        <v>0.9057307513772597</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3584,22 +3584,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1119464847722361</v>
+        <v>0.1129564847722361</v>
       </c>
       <c r="C27">
-        <v>290.1001970649118</v>
+        <v>278.3778766425046</v>
       </c>
       <c r="D27">
-        <v>423.5991970649118</v>
+        <v>417.2284766425046</v>
       </c>
       <c r="E27">
-        <v>127.03</v>
+        <v>132.3816</v>
       </c>
       <c r="F27">
-        <v>133.79</v>
+        <v>139.1416</v>
       </c>
       <c r="G27">
         <v>0.291</v>
@@ -3620,37 +3620,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M27">
-        <v>19.640372</v>
+        <v>20.42598688</v>
       </c>
       <c r="N27">
-        <v>-1.851483111111108</v>
+        <v>-2.637097991111109</v>
       </c>
       <c r="O27">
-        <v>-0.462870777777777</v>
+        <v>-0.6592744977777771</v>
       </c>
       <c r="P27">
-        <v>-1.388612333333331</v>
+        <v>-1.977823493333331</v>
       </c>
       <c r="Q27">
-        <v>-0.2886123333333313</v>
+        <v>-0.8778234933333318</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.11140875255483</v>
+        <v>0.1122953573190844</v>
       </c>
       <c r="T27">
-        <v>0.6344867808197518</v>
+        <v>0.6430609265065054</v>
       </c>
       <c r="U27">
         <v>0.1468</v>
       </c>
       <c r="V27">
-        <v>0.2264326878443149</v>
+        <v>0.2177237383118412</v>
       </c>
       <c r="W27">
-        <v>0.1135596814244546</v>
+        <v>0.1148381552158217</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.9057307513772597</v>
+        <v>0.870894953247365</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3666,22 +3666,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1129564847722361</v>
+        <v>0.1139664847722361</v>
       </c>
       <c r="C28">
-        <v>278.3778766425046</v>
+        <v>266.8443418864885</v>
       </c>
       <c r="D28">
-        <v>417.2284766425046</v>
+        <v>411.0465418864885</v>
       </c>
       <c r="E28">
-        <v>132.3816</v>
+        <v>137.7332</v>
       </c>
       <c r="F28">
-        <v>139.1416</v>
+        <v>144.4932</v>
       </c>
       <c r="G28">
         <v>0.291</v>
@@ -3702,37 +3702,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M28">
-        <v>20.42598688</v>
+        <v>21.21160176</v>
       </c>
       <c r="N28">
-        <v>-2.637097991111109</v>
+        <v>-3.422712871111109</v>
       </c>
       <c r="O28">
-        <v>-0.6592744977777771</v>
+        <v>-0.8556782177777773</v>
       </c>
       <c r="P28">
-        <v>-1.977823493333331</v>
+        <v>-2.567034653333332</v>
       </c>
       <c r="Q28">
-        <v>-0.8778234933333318</v>
+        <v>-1.467034653333332</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1122953573190844</v>
+        <v>0.1132062526248253</v>
       </c>
       <c r="T28">
-        <v>0.6430609265065054</v>
+        <v>0.6518699802942657</v>
       </c>
       <c r="U28">
         <v>0.1468</v>
       </c>
       <c r="V28">
-        <v>0.2177237383118412</v>
+        <v>0.2096598961521434</v>
       </c>
       <c r="W28">
-        <v>0.1148381552158217</v>
+        <v>0.1160219272448654</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.870894953247365</v>
+        <v>0.8386395846085737</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3748,22 +3748,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1139664847722361</v>
+        <v>0.1149764847722361</v>
       </c>
       <c r="C29">
-        <v>266.8443418864885</v>
+        <v>255.4913237937326</v>
       </c>
       <c r="D29">
-        <v>411.0465418864885</v>
+        <v>405.0451237937326</v>
       </c>
       <c r="E29">
-        <v>137.7332</v>
+        <v>143.0848</v>
       </c>
       <c r="F29">
-        <v>144.4932</v>
+        <v>149.8448</v>
       </c>
       <c r="G29">
         <v>0.291</v>
@@ -3784,37 +3784,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M29">
-        <v>21.21160176</v>
+        <v>21.99721664</v>
       </c>
       <c r="N29">
-        <v>-3.422712871111109</v>
+        <v>-4.20832775111111</v>
       </c>
       <c r="O29">
-        <v>-0.8556782177777773</v>
+        <v>-1.052081937777777</v>
       </c>
       <c r="P29">
-        <v>-2.567034653333332</v>
+        <v>-3.156245813333332</v>
       </c>
       <c r="Q29">
-        <v>-1.467034653333332</v>
+        <v>-2.056245813333333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1132062526248253</v>
+        <v>0.1141424505779479</v>
       </c>
       <c r="T29">
-        <v>0.6518699802942657</v>
+        <v>0.660923730020575</v>
       </c>
       <c r="U29">
         <v>0.1468</v>
       </c>
       <c r="V29">
-        <v>0.2096598961521434</v>
+        <v>0.2021720427181383</v>
       </c>
       <c r="W29">
-        <v>0.1160219272448654</v>
+        <v>0.1171211441289773</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.8386395846085737</v>
+        <v>0.8086881708725532</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3830,22 +3830,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1149764847722361</v>
+        <v>0.1324405206311405</v>
       </c>
       <c r="C30">
-        <v>255.4913237937326</v>
+        <v>168.4952171024183</v>
       </c>
       <c r="D30">
-        <v>405.0451237937326</v>
+        <v>323.4006171024183</v>
       </c>
       <c r="E30">
-        <v>143.0848</v>
+        <v>148.4364</v>
       </c>
       <c r="F30">
-        <v>149.8448</v>
+        <v>155.1964</v>
       </c>
       <c r="G30">
         <v>0.291</v>
@@ -3866,45 +3866,45 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M30">
-        <v>21.99721664</v>
+        <v>31.16343712</v>
       </c>
       <c r="N30">
-        <v>-4.20832775111111</v>
+        <v>-13.37454823111111</v>
       </c>
       <c r="O30">
-        <v>-1.052081937777777</v>
+        <v>-3.343637057777778</v>
       </c>
       <c r="P30">
-        <v>-3.156245813333332</v>
+        <v>-10.03091117333333</v>
       </c>
       <c r="Q30">
-        <v>-2.056245813333333</v>
+        <v>-8.930911173333335</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1141424505779479</v>
+        <v>0.1162233806690519</v>
       </c>
       <c r="T30">
-        <v>0.660923730020575</v>
+        <v>0.6810479144197847</v>
       </c>
       <c r="U30">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.2021720427181383</v>
+        <v>0.1427064096010159</v>
       </c>
       <c r="W30">
-        <v>0.1171211441289773</v>
+        <v>0.172144552952116</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y30">
-        <v>0.8086881708725532</v>
+        <v>0.5708256384040635</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3912,22 +3912,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1324405206311405</v>
+        <v>0.1339905206311405</v>
       </c>
       <c r="C31">
-        <v>168.4952171024183</v>
+        <v>157.459662036484</v>
       </c>
       <c r="D31">
-        <v>323.4006171024183</v>
+        <v>317.716662036484</v>
       </c>
       <c r="E31">
-        <v>148.4364</v>
+        <v>153.788</v>
       </c>
       <c r="F31">
-        <v>155.1964</v>
+        <v>160.548</v>
       </c>
       <c r="G31">
         <v>0.291</v>
@@ -3948,37 +3948,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M31">
-        <v>31.16343712</v>
+        <v>32.23803839999999</v>
       </c>
       <c r="N31">
-        <v>-13.37454823111111</v>
+        <v>-14.4491495111111</v>
       </c>
       <c r="O31">
-        <v>-3.343637057777777</v>
+        <v>-3.612287377777776</v>
       </c>
       <c r="P31">
-        <v>-10.03091117333333</v>
+        <v>-10.83686213333333</v>
       </c>
       <c r="Q31">
-        <v>-8.93091117333333</v>
+        <v>-9.736862133333327</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1162233806690519</v>
+        <v>0.1172294289643241</v>
       </c>
       <c r="T31">
-        <v>0.6810479144197847</v>
+        <v>0.6907771703400674</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.1427064096010159</v>
+        <v>0.1379495292809821</v>
       </c>
       <c r="W31">
-        <v>0.172144552952116</v>
+        <v>0.1730997345203788</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.5708256384040635</v>
+        <v>0.5517981171239281</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3994,22 +3994,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1339905206311405</v>
+        <v>0.1355405206311405</v>
       </c>
       <c r="C32">
-        <v>157.459662036484</v>
+        <v>146.6204537331992</v>
       </c>
       <c r="D32">
-        <v>317.716662036484</v>
+        <v>312.2290537331992</v>
       </c>
       <c r="E32">
-        <v>153.788</v>
+        <v>159.1396</v>
       </c>
       <c r="F32">
-        <v>160.548</v>
+        <v>165.8996</v>
       </c>
       <c r="G32">
         <v>0.291</v>
@@ -4030,37 +4030,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M32">
-        <v>32.23803839999999</v>
+        <v>33.31263968</v>
       </c>
       <c r="N32">
-        <v>-14.4491495111111</v>
+        <v>-15.52375079111111</v>
       </c>
       <c r="O32">
-        <v>-3.612287377777776</v>
+        <v>-3.880937697777776</v>
       </c>
       <c r="P32">
-        <v>-10.83686213333333</v>
+        <v>-11.64281309333333</v>
       </c>
       <c r="Q32">
-        <v>-9.736862133333327</v>
+        <v>-10.54281309333333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1172294289643241</v>
+        <v>0.118264638079749</v>
       </c>
       <c r="T32">
-        <v>0.6907771703400674</v>
+        <v>0.7007884336783292</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.1379495292809821</v>
+        <v>0.1334995444654665</v>
       </c>
       <c r="W32">
-        <v>0.1730997345203788</v>
+        <v>0.1739932914713343</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.5517981171239281</v>
+        <v>0.5339981778618659</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4076,22 +4076,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1355405206311405</v>
+        <v>0.1370905206311405</v>
       </c>
       <c r="C33">
-        <v>146.6204537331992</v>
+        <v>135.9675910178525</v>
       </c>
       <c r="D33">
-        <v>312.2290537331992</v>
+        <v>306.9277910178525</v>
       </c>
       <c r="E33">
-        <v>159.1396</v>
+        <v>164.4912</v>
       </c>
       <c r="F33">
-        <v>165.8996</v>
+        <v>171.2512</v>
       </c>
       <c r="G33">
         <v>0.291</v>
@@ -4112,37 +4112,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M33">
-        <v>33.31263968</v>
+        <v>34.38724096</v>
       </c>
       <c r="N33">
-        <v>-15.52375079111111</v>
+        <v>-16.59835207111111</v>
       </c>
       <c r="O33">
-        <v>-3.880937697777776</v>
+        <v>-4.149588017777777</v>
       </c>
       <c r="P33">
-        <v>-11.64281309333333</v>
+        <v>-12.44876405333333</v>
       </c>
       <c r="Q33">
-        <v>-10.54281309333333</v>
+        <v>-11.34876405333333</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.118264638079749</v>
+        <v>0.1193302945220983</v>
       </c>
       <c r="T33">
-        <v>0.7007884336783292</v>
+        <v>0.7110941459383047</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.1334995444654665</v>
+        <v>0.1293276837009207</v>
       </c>
       <c r="W33">
-        <v>0.1739932914713343</v>
+        <v>0.1748310011128552</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.5339981778618659</v>
+        <v>0.5173107348036826</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4158,22 +4158,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1370905206311405</v>
+        <v>0.1386405206311405</v>
       </c>
       <c r="C34">
-        <v>135.9675910178525</v>
+        <v>125.4917406060328</v>
       </c>
       <c r="D34">
-        <v>306.9277910178525</v>
+        <v>301.8035406060328</v>
       </c>
       <c r="E34">
-        <v>164.4912</v>
+        <v>169.8428</v>
       </c>
       <c r="F34">
-        <v>171.2512</v>
+        <v>176.6028</v>
       </c>
       <c r="G34">
         <v>0.291</v>
@@ -4194,37 +4194,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M34">
-        <v>34.38724096</v>
+        <v>35.46184224</v>
       </c>
       <c r="N34">
-        <v>-16.59835207111111</v>
+        <v>-17.67295335111111</v>
       </c>
       <c r="O34">
-        <v>-4.149588017777777</v>
+        <v>-4.418238337777778</v>
       </c>
       <c r="P34">
-        <v>-12.44876405333333</v>
+        <v>-13.25471501333333</v>
       </c>
       <c r="Q34">
-        <v>-11.34876405333333</v>
+        <v>-12.15471501333333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1193302945220983</v>
+        <v>0.1204277616045177</v>
       </c>
       <c r="T34">
-        <v>0.7110941459383047</v>
+        <v>0.7217074914000704</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.1293276837009207</v>
+        <v>0.1254086629827109</v>
       </c>
       <c r="W34">
-        <v>0.1748310011128552</v>
+        <v>0.1756179404730717</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.5173107348036826</v>
+        <v>0.5016346519308437</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4240,22 +4240,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1386405206311405</v>
+        <v>0.152410923691098</v>
       </c>
       <c r="C35">
-        <v>125.4917406060328</v>
+        <v>81.1576775039488</v>
       </c>
       <c r="D35">
-        <v>301.8035406060328</v>
+        <v>262.8210775039488</v>
       </c>
       <c r="E35">
-        <v>169.8428</v>
+        <v>175.1944</v>
       </c>
       <c r="F35">
-        <v>176.6028</v>
+        <v>181.9544</v>
       </c>
       <c r="G35">
         <v>0.291</v>
@@ -4276,45 +4276,45 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M35">
-        <v>35.46184224</v>
+        <v>42.90484752</v>
       </c>
       <c r="N35">
-        <v>-17.67295335111111</v>
+        <v>-25.11595863111111</v>
       </c>
       <c r="O35">
-        <v>-4.418238337777778</v>
+        <v>-6.278989657777776</v>
       </c>
       <c r="P35">
-        <v>-13.25471501333333</v>
+        <v>-18.83696897333333</v>
       </c>
       <c r="Q35">
-        <v>-12.15471501333333</v>
+        <v>-17.73696897333333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1204277616045177</v>
+        <v>0.1220439444469459</v>
       </c>
       <c r="T35">
-        <v>0.7217074914000704</v>
+        <v>0.7373372147064455</v>
       </c>
       <c r="U35">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.1254086629827109</v>
+        <v>0.1036531412947957</v>
       </c>
       <c r="W35">
-        <v>0.1756179404730717</v>
+        <v>0.2113585892826872</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.5016346519308437</v>
+        <v>0.4146125651791827</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4322,22 +4322,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.152410923691098</v>
+        <v>0.1543109236910979</v>
       </c>
       <c r="C36">
-        <v>81.1576775039488</v>
+        <v>71.2041440739188</v>
       </c>
       <c r="D36">
-        <v>262.8210775039488</v>
+        <v>258.2191440739188</v>
       </c>
       <c r="E36">
-        <v>175.1944</v>
+        <v>180.546</v>
       </c>
       <c r="F36">
-        <v>181.9544</v>
+        <v>187.306</v>
       </c>
       <c r="G36">
         <v>0.291</v>
@@ -4358,37 +4358,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M36">
-        <v>42.90484752</v>
+        <v>44.16675480000001</v>
       </c>
       <c r="N36">
-        <v>-25.11595863111111</v>
+        <v>-26.37786591111112</v>
       </c>
       <c r="O36">
-        <v>-6.278989657777776</v>
+        <v>-6.594466477777779</v>
       </c>
       <c r="P36">
-        <v>-18.83696897333333</v>
+        <v>-19.78339943333334</v>
       </c>
       <c r="Q36">
-        <v>-17.73696897333333</v>
+        <v>-18.68339943333334</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1220439444469459</v>
+        <v>0.1232169282076682</v>
       </c>
       <c r="T36">
-        <v>0.7373372147064455</v>
+        <v>0.7486808641634678</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.1036531412947957</v>
+        <v>0.1006916229720872</v>
       </c>
       <c r="W36">
-        <v>0.2113585892826872</v>
+        <v>0.2120569153031819</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.4146125651791827</v>
+        <v>0.4027664918883488</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4404,22 +4404,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1543109236910979</v>
+        <v>0.156210923691098</v>
       </c>
       <c r="C37">
-        <v>71.2041440739188</v>
+        <v>61.40899485488441</v>
       </c>
       <c r="D37">
-        <v>258.2191440739188</v>
+        <v>253.7755948548844</v>
       </c>
       <c r="E37">
-        <v>180.546</v>
+        <v>185.8976</v>
       </c>
       <c r="F37">
-        <v>187.306</v>
+        <v>192.6576</v>
       </c>
       <c r="G37">
         <v>0.291</v>
@@ -4440,37 +4440,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M37">
-        <v>44.16675480000001</v>
+        <v>45.42866208</v>
       </c>
       <c r="N37">
-        <v>-26.37786591111112</v>
+        <v>-27.63977319111111</v>
       </c>
       <c r="O37">
-        <v>-6.594466477777779</v>
+        <v>-6.909943297777778</v>
       </c>
       <c r="P37">
-        <v>-19.78339943333334</v>
+        <v>-20.72982989333333</v>
       </c>
       <c r="Q37">
-        <v>-18.68339943333334</v>
+        <v>-19.62982989333333</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1232169282076682</v>
+        <v>0.124426567710913</v>
       </c>
       <c r="T37">
-        <v>0.7486808641634678</v>
+        <v>0.7603790026660221</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.1006916229720872</v>
+        <v>0.09789463344508478</v>
       </c>
       <c r="W37">
-        <v>0.2120569153031819</v>
+        <v>0.212716445433649</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.4027664918883488</v>
+        <v>0.3915785337803391</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4486,22 +4486,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.156210923691098</v>
+        <v>0.158110923691098</v>
       </c>
       <c r="C38">
-        <v>61.40899485488444</v>
+        <v>51.76419153700891</v>
       </c>
       <c r="D38">
-        <v>253.7755948548844</v>
+        <v>249.4823915370089</v>
       </c>
       <c r="E38">
-        <v>185.8976</v>
+        <v>191.2492</v>
       </c>
       <c r="F38">
-        <v>192.6576</v>
+        <v>198.0092</v>
       </c>
       <c r="G38">
         <v>0.291</v>
@@ -4522,37 +4522,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M38">
-        <v>45.42866208</v>
+        <v>46.69056936</v>
       </c>
       <c r="N38">
-        <v>-27.6397731911111</v>
+        <v>-28.90168047111111</v>
       </c>
       <c r="O38">
-        <v>-6.909943297777776</v>
+        <v>-7.225420117777777</v>
       </c>
       <c r="P38">
-        <v>-20.72982989333333</v>
+        <v>-21.67626035333333</v>
       </c>
       <c r="Q38">
-        <v>-19.62982989333333</v>
+        <v>-20.57626035333333</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.124426567710913</v>
+        <v>0.1256746084682291</v>
       </c>
       <c r="T38">
-        <v>0.760379002666022</v>
+        <v>0.7724485106448478</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.0978946334450848</v>
+        <v>0.09524883254116358</v>
       </c>
       <c r="W38">
-        <v>0.212716445433649</v>
+        <v>0.2133403252867936</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3915785337803391</v>
+        <v>0.3809953301646543</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4568,22 +4568,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.158110923691098</v>
+        <v>0.160010923691098</v>
       </c>
       <c r="C39">
-        <v>51.76419153700891</v>
+        <v>42.26223070810627</v>
       </c>
       <c r="D39">
-        <v>249.4823915370089</v>
+        <v>245.3320307081063</v>
       </c>
       <c r="E39">
-        <v>191.2492</v>
+        <v>196.6008</v>
       </c>
       <c r="F39">
-        <v>198.0092</v>
+        <v>203.3608</v>
       </c>
       <c r="G39">
         <v>0.291</v>
@@ -4604,37 +4604,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M39">
-        <v>46.69056936</v>
+        <v>47.95247664</v>
       </c>
       <c r="N39">
-        <v>-28.90168047111111</v>
+        <v>-30.16358775111111</v>
       </c>
       <c r="O39">
-        <v>-7.225420117777777</v>
+        <v>-7.540896937777777</v>
       </c>
       <c r="P39">
-        <v>-21.67626035333333</v>
+        <v>-22.62269081333333</v>
       </c>
       <c r="Q39">
-        <v>-20.57626035333333</v>
+        <v>-21.52269081333333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1256746084682291</v>
+        <v>0.1269629086048134</v>
       </c>
       <c r="T39">
-        <v>0.7724485106448478</v>
+        <v>0.7849073575907324</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.09524883254116358</v>
+        <v>0.09274228431639611</v>
       </c>
       <c r="W39">
-        <v>0.2133403252867936</v>
+        <v>0.2139313693581938</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3809953301646543</v>
+        <v>0.3709691372655844</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4650,22 +4650,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.160010923691098</v>
+        <v>0.1619109236910979</v>
       </c>
       <c r="C40">
-        <v>42.26223070810627</v>
+        <v>32.8961000892173</v>
       </c>
       <c r="D40">
-        <v>245.3320307081063</v>
+        <v>241.3175000892173</v>
       </c>
       <c r="E40">
-        <v>196.6008</v>
+        <v>201.9524</v>
       </c>
       <c r="F40">
-        <v>203.3608</v>
+        <v>208.7124</v>
       </c>
       <c r="G40">
         <v>0.291</v>
@@ -4686,37 +4686,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M40">
-        <v>47.95247664</v>
+        <v>49.21438392</v>
       </c>
       <c r="N40">
-        <v>-30.16358775111111</v>
+        <v>-31.42549503111111</v>
       </c>
       <c r="O40">
-        <v>-7.540896937777777</v>
+        <v>-7.856373757777778</v>
       </c>
       <c r="P40">
-        <v>-22.62269081333333</v>
+        <v>-23.56912127333333</v>
       </c>
       <c r="Q40">
-        <v>-21.52269081333333</v>
+        <v>-22.46912127333334</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1269629086048134</v>
+        <v>0.1282934480901382</v>
       </c>
       <c r="T40">
-        <v>0.7849073575907324</v>
+        <v>0.797774691321728</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.09274228431639611</v>
+        <v>0.09036427702623211</v>
       </c>
       <c r="W40">
-        <v>0.2139313693581938</v>
+        <v>0.2144921034772145</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3709691372655844</v>
+        <v>0.3614571081049284</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4732,22 +4732,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1619109236910979</v>
+        <v>0.163810923691098</v>
       </c>
       <c r="C41">
-        <v>32.8961000892173</v>
+        <v>23.6592389978824</v>
       </c>
       <c r="D41">
-        <v>241.3175000892173</v>
+        <v>237.4322389978824</v>
       </c>
       <c r="E41">
-        <v>201.9524</v>
+        <v>207.304</v>
       </c>
       <c r="F41">
-        <v>208.7124</v>
+        <v>214.064</v>
       </c>
       <c r="G41">
         <v>0.291</v>
@@ -4768,37 +4768,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M41">
-        <v>49.21438392</v>
+        <v>50.4762912</v>
       </c>
       <c r="N41">
-        <v>-31.42549503111111</v>
+        <v>-32.68740231111111</v>
       </c>
       <c r="O41">
-        <v>-7.856373757777778</v>
+        <v>-8.171850577777777</v>
       </c>
       <c r="P41">
-        <v>-23.56912127333333</v>
+        <v>-24.51555173333333</v>
       </c>
       <c r="Q41">
-        <v>-22.46912127333334</v>
+        <v>-23.41555173333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1282934480901382</v>
+        <v>0.1296683388916405</v>
       </c>
       <c r="T41">
-        <v>0.797774691321728</v>
+        <v>0.8110709361770901</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.09036427702623211</v>
+        <v>0.08810517010057631</v>
       </c>
       <c r="W41">
-        <v>0.2144921034772145</v>
+        <v>0.2150248008902841</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3614571081049284</v>
+        <v>0.3524206804023052</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4814,22 +4814,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.163810923691098</v>
+        <v>0.165710923691098</v>
       </c>
       <c r="C42">
-        <v>23.6592389978824</v>
+        <v>14.54550257019451</v>
       </c>
       <c r="D42">
-        <v>237.4322389978824</v>
+        <v>233.6701025701945</v>
       </c>
       <c r="E42">
-        <v>207.304</v>
+        <v>212.6556</v>
       </c>
       <c r="F42">
-        <v>214.064</v>
+        <v>219.4156</v>
       </c>
       <c r="G42">
         <v>0.291</v>
@@ -4850,37 +4850,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M42">
-        <v>50.4762912</v>
+        <v>51.73819848000001</v>
       </c>
       <c r="N42">
-        <v>-32.68740231111111</v>
+        <v>-33.94930959111112</v>
       </c>
       <c r="O42">
-        <v>-8.171850577777777</v>
+        <v>-8.487327397777779</v>
       </c>
       <c r="P42">
-        <v>-24.51555173333333</v>
+        <v>-25.46198219333334</v>
       </c>
       <c r="Q42">
-        <v>-23.41555173333333</v>
+        <v>-24.36198219333334</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1296683388916405</v>
+        <v>0.1310898361609904</v>
       </c>
       <c r="T42">
-        <v>0.8110709361770901</v>
+        <v>0.8248179011970408</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.08810517010057631</v>
+        <v>0.08595626351275736</v>
       </c>
       <c r="W42">
-        <v>0.2150248008902841</v>
+        <v>0.2155315130636918</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3524206804023052</v>
+        <v>0.3438250540510295</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4896,22 +4896,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.165710923691098</v>
+        <v>0.167610923691098</v>
       </c>
       <c r="C43">
-        <v>14.54550257019451</v>
+        <v>5.549129331225799</v>
       </c>
       <c r="D43">
-        <v>233.6701025701945</v>
+        <v>230.0253293312258</v>
       </c>
       <c r="E43">
-        <v>212.6556</v>
+        <v>218.0072</v>
       </c>
       <c r="F43">
-        <v>219.4156</v>
+        <v>224.7672</v>
       </c>
       <c r="G43">
         <v>0.291</v>
@@ -4932,37 +4932,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M43">
-        <v>51.73819848000001</v>
+        <v>53.00010576</v>
       </c>
       <c r="N43">
-        <v>-33.94930959111112</v>
+        <v>-35.21121687111111</v>
       </c>
       <c r="O43">
-        <v>-8.487327397777779</v>
+        <v>-8.802804217777778</v>
       </c>
       <c r="P43">
-        <v>-25.46198219333334</v>
+        <v>-26.40841265333334</v>
       </c>
       <c r="Q43">
-        <v>-24.36198219333334</v>
+        <v>-25.30841265333333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1310898361609904</v>
+        <v>0.1325603505775592</v>
       </c>
       <c r="T43">
-        <v>0.8248179011970408</v>
+        <v>0.8390388994935415</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.08595626351275736</v>
+        <v>0.08390968581007266</v>
       </c>
       <c r="W43">
-        <v>0.2155315130636918</v>
+        <v>0.2160140960859849</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3438250540510295</v>
+        <v>0.3356387432402906</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4978,22 +4978,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.167610923691098</v>
+        <v>0.169510923691098</v>
       </c>
       <c r="C44">
-        <v>5.549129331225828</v>
+        <v>-3.335288246150071</v>
       </c>
       <c r="D44">
-        <v>230.0253293312258</v>
+        <v>226.4925117538499</v>
       </c>
       <c r="E44">
-        <v>218.0072</v>
+        <v>223.3588</v>
       </c>
       <c r="F44">
-        <v>224.7672</v>
+        <v>230.1188</v>
       </c>
       <c r="G44">
         <v>0.291</v>
@@ -5014,37 +5014,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M44">
-        <v>53.00010576</v>
+        <v>54.26201304</v>
       </c>
       <c r="N44">
-        <v>-35.21121687111111</v>
+        <v>-36.47312415111111</v>
       </c>
       <c r="O44">
-        <v>-8.802804217777776</v>
+        <v>-9.118281037777777</v>
       </c>
       <c r="P44">
-        <v>-26.40841265333333</v>
+        <v>-27.35484311333333</v>
       </c>
       <c r="Q44">
-        <v>-25.30841265333333</v>
+        <v>-26.25484311333333</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1325603505775592</v>
+        <v>0.1340824619912006</v>
       </c>
       <c r="T44">
-        <v>0.8390388994935414</v>
+        <v>0.8537588801864106</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.08390968581007267</v>
+        <v>0.08195829776797796</v>
       </c>
       <c r="W44">
-        <v>0.2160140960859849</v>
+        <v>0.2164742333863108</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3356387432402907</v>
+        <v>0.3278331910719119</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5060,22 +5060,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.169510923691098</v>
+        <v>0.1714109236910979</v>
       </c>
       <c r="C45">
-        <v>-3.335288246150071</v>
+        <v>-12.11283051045979</v>
       </c>
       <c r="D45">
-        <v>226.4925117538499</v>
+        <v>223.0665694895402</v>
       </c>
       <c r="E45">
-        <v>223.3588</v>
+        <v>228.7104</v>
       </c>
       <c r="F45">
-        <v>230.1188</v>
+        <v>235.4704</v>
       </c>
       <c r="G45">
         <v>0.291</v>
@@ -5096,37 +5096,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M45">
-        <v>54.26201304</v>
+        <v>55.52392031999999</v>
       </c>
       <c r="N45">
-        <v>-36.47312415111111</v>
+        <v>-37.7350314311111</v>
       </c>
       <c r="O45">
-        <v>-9.118281037777777</v>
+        <v>-9.433757857777776</v>
       </c>
       <c r="P45">
-        <v>-27.35484311333333</v>
+        <v>-28.30127357333333</v>
       </c>
       <c r="Q45">
-        <v>-26.25484311333333</v>
+        <v>-27.20127357333332</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1340824619912006</v>
+        <v>0.1356589345267577</v>
       </c>
       <c r="T45">
-        <v>0.8537588801864106</v>
+        <v>0.8690045744754535</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.08195829776797796</v>
+        <v>0.0800956091823421</v>
       </c>
       <c r="W45">
-        <v>0.2164742333863108</v>
+        <v>0.2169134553548037</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3278331910719119</v>
+        <v>0.3203824367293684</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5142,22 +5142,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1714109236910979</v>
+        <v>0.173310923691098</v>
       </c>
       <c r="C46">
-        <v>-12.11283051045979</v>
+        <v>-20.78827500755457</v>
       </c>
       <c r="D46">
-        <v>223.0665694895402</v>
+        <v>219.7427249924454</v>
       </c>
       <c r="E46">
-        <v>228.7104</v>
+        <v>234.062</v>
       </c>
       <c r="F46">
-        <v>235.4704</v>
+        <v>240.822</v>
       </c>
       <c r="G46">
         <v>0.291</v>
@@ -5178,37 +5178,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M46">
-        <v>55.52392031999999</v>
+        <v>56.7858276</v>
       </c>
       <c r="N46">
-        <v>-37.7350314311111</v>
+        <v>-38.99693871111111</v>
       </c>
       <c r="O46">
-        <v>-9.433757857777776</v>
+        <v>-9.749234677777778</v>
       </c>
       <c r="P46">
-        <v>-28.30127357333333</v>
+        <v>-29.24770403333333</v>
       </c>
       <c r="Q46">
-        <v>-27.20127357333332</v>
+        <v>-28.14770403333333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1356589345267577</v>
+        <v>0.1372927333363351</v>
       </c>
       <c r="T46">
-        <v>0.8690045744754535</v>
+        <v>0.8848046576477346</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.0800956091823421</v>
+        <v>0.07831570675606782</v>
       </c>
       <c r="W46">
-        <v>0.2169134553548037</v>
+        <v>0.2173331563469192</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3203824367293684</v>
+        <v>0.3132628270242713</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5224,22 +5224,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.173310923691098</v>
+        <v>0.175210923691098</v>
       </c>
       <c r="C47">
-        <v>-20.78827500755457</v>
+        <v>-29.36611870922414</v>
       </c>
       <c r="D47">
-        <v>219.7427249924454</v>
+        <v>216.5164812907759</v>
       </c>
       <c r="E47">
-        <v>234.062</v>
+        <v>239.4136</v>
       </c>
       <c r="F47">
-        <v>240.822</v>
+        <v>246.1736</v>
       </c>
       <c r="G47">
         <v>0.291</v>
@@ -5260,37 +5260,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M47">
-        <v>56.7858276</v>
+        <v>58.04773488</v>
       </c>
       <c r="N47">
-        <v>-38.99693871111111</v>
+        <v>-40.25884599111111</v>
       </c>
       <c r="O47">
-        <v>-9.749234677777778</v>
+        <v>-10.06471149777778</v>
       </c>
       <c r="P47">
-        <v>-29.24770403333333</v>
+        <v>-30.19413449333333</v>
       </c>
       <c r="Q47">
-        <v>-28.14770403333333</v>
+        <v>-29.09413449333333</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1372927333363351</v>
+        <v>0.1389870432129339</v>
       </c>
       <c r="T47">
-        <v>0.8848046576477346</v>
+        <v>0.9011899290856556</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.07831570675606782</v>
+        <v>0.07661319139180549</v>
       </c>
       <c r="W47">
-        <v>0.2173331563469192</v>
+        <v>0.2177346094698123</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3132628270242713</v>
+        <v>0.3064527655672219</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5306,22 +5306,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.175210923691098</v>
+        <v>0.177110923691098</v>
       </c>
       <c r="C48">
-        <v>-29.36611870922414</v>
+        <v>-37.85059831199226</v>
       </c>
       <c r="D48">
-        <v>216.5164812907759</v>
+        <v>213.3836016880078</v>
       </c>
       <c r="E48">
-        <v>239.4136</v>
+        <v>244.7652</v>
       </c>
       <c r="F48">
-        <v>246.1736</v>
+        <v>251.5252</v>
       </c>
       <c r="G48">
         <v>0.291</v>
@@ -5342,37 +5342,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M48">
-        <v>58.04773488</v>
+        <v>59.30964216</v>
       </c>
       <c r="N48">
-        <v>-40.25884599111111</v>
+        <v>-41.52075327111111</v>
       </c>
       <c r="O48">
-        <v>-10.06471149777778</v>
+        <v>-10.38018831777778</v>
       </c>
       <c r="P48">
-        <v>-30.19413449333333</v>
+        <v>-31.14056495333333</v>
       </c>
       <c r="Q48">
-        <v>-29.09413449333333</v>
+        <v>-30.04056495333333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1389870432129339</v>
+        <v>0.1407452893112912</v>
       </c>
       <c r="T48">
-        <v>0.9011899290856556</v>
+        <v>0.9181935126533095</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.07661319139180549</v>
+        <v>0.07498312348985217</v>
       </c>
       <c r="W48">
-        <v>0.2177346094698123</v>
+        <v>0.2181189794810929</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3064527655672219</v>
+        <v>0.2999324939594087</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5388,22 +5388,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.177110923691098</v>
+        <v>0.179010923691098</v>
       </c>
       <c r="C49">
-        <v>-37.85059831199226</v>
+        <v>-46.24570879877001</v>
       </c>
       <c r="D49">
-        <v>213.3836016880078</v>
+        <v>210.34009120123</v>
       </c>
       <c r="E49">
-        <v>244.7652</v>
+        <v>250.1168</v>
       </c>
       <c r="F49">
-        <v>251.5252</v>
+        <v>256.8768</v>
       </c>
       <c r="G49">
         <v>0.291</v>
@@ -5424,37 +5424,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M49">
-        <v>59.30964216</v>
+        <v>60.57154944000001</v>
       </c>
       <c r="N49">
-        <v>-41.52075327111111</v>
+        <v>-42.78266055111111</v>
       </c>
       <c r="O49">
-        <v>-10.38018831777778</v>
+        <v>-10.69566513777778</v>
       </c>
       <c r="P49">
-        <v>-31.14056495333333</v>
+        <v>-32.08699541333333</v>
       </c>
       <c r="Q49">
-        <v>-30.04056495333333</v>
+        <v>-30.98699541333333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1407452893112912</v>
+        <v>0.1425711602595852</v>
       </c>
       <c r="T49">
-        <v>0.9181935126533095</v>
+        <v>0.9358510802043348</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.07498312348985217</v>
+        <v>0.07342097508381358</v>
       </c>
       <c r="W49">
-        <v>0.2181189794810929</v>
+        <v>0.2184873340752368</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2999324939594087</v>
+        <v>0.2936839003352544</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5470,22 +5470,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1790109236910979</v>
+        <v>0.180910923691098</v>
       </c>
       <c r="C50">
-        <v>-46.24570879877001</v>
+        <v>-54.55522043436835</v>
       </c>
       <c r="D50">
-        <v>210.34009120123</v>
+        <v>207.3821795656316</v>
       </c>
       <c r="E50">
-        <v>250.1168</v>
+        <v>255.4684</v>
       </c>
       <c r="F50">
-        <v>256.8768</v>
+        <v>262.2284</v>
       </c>
       <c r="G50">
         <v>0.291</v>
@@ -5506,37 +5506,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M50">
-        <v>60.57154944000001</v>
+        <v>61.83345671999999</v>
       </c>
       <c r="N50">
-        <v>-42.78266055111111</v>
+        <v>-44.0445678311111</v>
       </c>
       <c r="O50">
-        <v>-10.69566513777778</v>
+        <v>-11.01114195777778</v>
       </c>
       <c r="P50">
-        <v>-32.08699541333333</v>
+        <v>-33.03342587333333</v>
       </c>
       <c r="Q50">
-        <v>-30.98699541333333</v>
+        <v>-31.93342587333333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1425711602595852</v>
+        <v>0.1444686339901653</v>
       </c>
       <c r="T50">
-        <v>0.9358510802043347</v>
+        <v>0.9542011013848118</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.07342097508381358</v>
+        <v>0.07192258783720515</v>
       </c>
       <c r="W50">
-        <v>0.2184873340752368</v>
+        <v>0.218840653787987</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2936839003352544</v>
+        <v>0.2876903513488206</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5552,22 +5552,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.180910923691098</v>
+        <v>0.182810923691098</v>
       </c>
       <c r="C51">
-        <v>-54.55522043436835</v>
+        <v>-62.78269434689716</v>
       </c>
       <c r="D51">
-        <v>207.3821795656316</v>
+        <v>204.5063056531028</v>
       </c>
       <c r="E51">
-        <v>255.4684</v>
+        <v>260.82</v>
       </c>
       <c r="F51">
-        <v>262.2284</v>
+        <v>267.58</v>
       </c>
       <c r="G51">
         <v>0.291</v>
@@ -5588,37 +5588,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M51">
-        <v>61.83345671999999</v>
+        <v>63.095364</v>
       </c>
       <c r="N51">
-        <v>-44.0445678311111</v>
+        <v>-45.30647511111111</v>
       </c>
       <c r="O51">
-        <v>-11.01114195777778</v>
+        <v>-11.32661877777778</v>
       </c>
       <c r="P51">
-        <v>-33.03342587333333</v>
+        <v>-33.97985633333333</v>
       </c>
       <c r="Q51">
-        <v>-31.93342587333333</v>
+        <v>-32.87985633333333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1444686339901653</v>
+        <v>0.1464420066699686</v>
       </c>
       <c r="T51">
-        <v>0.9542011013848118</v>
+        <v>0.9732851234125081</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.07192258783720515</v>
+        <v>0.07048413608046104</v>
       </c>
       <c r="W51">
-        <v>0.218840653787987</v>
+        <v>0.2191798407122273</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2876903513488206</v>
+        <v>0.2819365443218442</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5634,22 +5634,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.182810923691098</v>
+        <v>0.184710923691098</v>
       </c>
       <c r="C52">
-        <v>-62.78269434689716</v>
+        <v>-70.93149683044663</v>
       </c>
       <c r="D52">
-        <v>204.5063056531028</v>
+        <v>201.7091031695534</v>
       </c>
       <c r="E52">
-        <v>260.82</v>
+        <v>266.1716</v>
       </c>
       <c r="F52">
-        <v>267.58</v>
+        <v>272.9316</v>
       </c>
       <c r="G52">
         <v>0.291</v>
@@ -5670,37 +5670,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M52">
-        <v>63.095364</v>
+        <v>64.35727128000001</v>
       </c>
       <c r="N52">
-        <v>-45.30647511111111</v>
+        <v>-46.56838239111111</v>
       </c>
       <c r="O52">
-        <v>-11.32661877777778</v>
+        <v>-11.64209559777778</v>
       </c>
       <c r="P52">
-        <v>-33.97985633333333</v>
+        <v>-34.92628679333333</v>
       </c>
       <c r="Q52">
-        <v>-32.87985633333333</v>
+        <v>-33.82628679333333</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1464420066699686</v>
+        <v>0.1484959251734374</v>
       </c>
       <c r="T52">
-        <v>0.9732851234125081</v>
+        <v>0.9931480851148042</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.07048413608046104</v>
+        <v>0.06910209419653043</v>
       </c>
       <c r="W52">
-        <v>0.2191798407122273</v>
+        <v>0.2195057261884581</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2819365443218442</v>
+        <v>0.2764083767861217</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5716,22 +5716,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.184710923691098</v>
+        <v>0.186610923691098</v>
       </c>
       <c r="C53">
-        <v>-70.93149683044663</v>
+        <v>-79.00481248982894</v>
       </c>
       <c r="D53">
-        <v>201.7091031695534</v>
+        <v>198.987387510171</v>
       </c>
       <c r="E53">
-        <v>266.1716</v>
+        <v>271.5232</v>
       </c>
       <c r="F53">
-        <v>272.9316</v>
+        <v>278.2832</v>
       </c>
       <c r="G53">
         <v>0.291</v>
@@ -5752,37 +5752,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M53">
-        <v>64.35727128000001</v>
+        <v>65.61917855999999</v>
       </c>
       <c r="N53">
-        <v>-46.56838239111111</v>
+        <v>-47.8302896711111</v>
       </c>
       <c r="O53">
-        <v>-11.64209559777778</v>
+        <v>-11.95757241777778</v>
       </c>
       <c r="P53">
-        <v>-34.92628679333333</v>
+        <v>-35.87271725333333</v>
       </c>
       <c r="Q53">
-        <v>-33.82628679333333</v>
+        <v>-34.77271725333333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1484959251734374</v>
+        <v>0.1506354236145507</v>
       </c>
       <c r="T53">
-        <v>0.9931480851148042</v>
+        <v>1.013838670221363</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.06910209419653043</v>
+        <v>0.06777320776967409</v>
       </c>
       <c r="W53">
-        <v>0.2195057261884581</v>
+        <v>0.2198190776079109</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2764083767861217</v>
+        <v>0.2710928310786963</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5798,22 +5798,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.186610923691098</v>
+        <v>0.188510923691098</v>
       </c>
       <c r="C54">
-        <v>-79.00481248982894</v>
+        <v>-87.00565633529445</v>
       </c>
       <c r="D54">
-        <v>198.987387510171</v>
+        <v>196.3381436647055</v>
       </c>
       <c r="E54">
-        <v>271.5232</v>
+        <v>276.8748</v>
       </c>
       <c r="F54">
-        <v>278.2832</v>
+        <v>283.6348</v>
       </c>
       <c r="G54">
         <v>0.291</v>
@@ -5834,37 +5834,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M54">
-        <v>65.61917855999999</v>
+        <v>66.88108584</v>
       </c>
       <c r="N54">
-        <v>-47.8302896711111</v>
+        <v>-49.09219695111111</v>
       </c>
       <c r="O54">
-        <v>-11.95757241777778</v>
+        <v>-12.27304923777778</v>
       </c>
       <c r="P54">
-        <v>-35.87271725333333</v>
+        <v>-36.81914771333333</v>
       </c>
       <c r="Q54">
-        <v>-34.77271725333333</v>
+        <v>-35.71914771333333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1506354236145507</v>
+        <v>0.1528659645425199</v>
       </c>
       <c r="T54">
-        <v>1.013838670221363</v>
+        <v>1.035409705757988</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.06777320776967409</v>
+        <v>0.06649446800043494</v>
       </c>
       <c r="W54">
-        <v>0.2198190776079109</v>
+        <v>0.2201206044454975</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2710928310786963</v>
+        <v>0.2659778720017398</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5880,22 +5880,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.188510923691098</v>
+        <v>0.190410923691098</v>
       </c>
       <c r="C55">
-        <v>-87.00565633529445</v>
+        <v>-94.93688492379431</v>
       </c>
       <c r="D55">
-        <v>196.3381436647055</v>
+        <v>193.7585150762057</v>
       </c>
       <c r="E55">
-        <v>276.8748</v>
+        <v>282.2264</v>
       </c>
       <c r="F55">
-        <v>283.6348</v>
+        <v>288.9864</v>
       </c>
       <c r="G55">
         <v>0.291</v>
@@ -5916,37 +5916,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M55">
-        <v>66.88108584</v>
+        <v>68.14299312</v>
       </c>
       <c r="N55">
-        <v>-49.09219695111111</v>
+        <v>-50.35410423111111</v>
       </c>
       <c r="O55">
-        <v>-12.27304923777778</v>
+        <v>-12.58852605777778</v>
       </c>
       <c r="P55">
-        <v>-36.81914771333333</v>
+        <v>-37.76557817333333</v>
       </c>
       <c r="Q55">
-        <v>-35.71914771333333</v>
+        <v>-36.66557817333333</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1528659645425199</v>
+        <v>0.1551934855108354</v>
       </c>
       <c r="T55">
-        <v>1.035409705757988</v>
+        <v>1.0579186124049</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.06649446800043494</v>
+        <v>0.06526308896338985</v>
       </c>
       <c r="W55">
-        <v>0.2201206044454975</v>
+        <v>0.2204109636224327</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2659778720017398</v>
+        <v>0.2610523558535595</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5962,22 +5962,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.190410923691098</v>
+        <v>0.192310923691098</v>
       </c>
       <c r="C56">
-        <v>-94.93688492379431</v>
+        <v>-102.801206633344</v>
       </c>
       <c r="D56">
-        <v>193.7585150762057</v>
+        <v>191.245793366656</v>
       </c>
       <c r="E56">
-        <v>282.2264</v>
+        <v>287.578</v>
       </c>
       <c r="F56">
-        <v>288.9864</v>
+        <v>294.338</v>
       </c>
       <c r="G56">
         <v>0.291</v>
@@ -5998,37 +5998,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M56">
-        <v>68.14299312</v>
+        <v>69.4049004</v>
       </c>
       <c r="N56">
-        <v>-50.35410423111111</v>
+        <v>-51.61601151111111</v>
       </c>
       <c r="O56">
-        <v>-12.58852605777778</v>
+        <v>-12.90400287777778</v>
       </c>
       <c r="P56">
-        <v>-37.76557817333333</v>
+        <v>-38.71200863333333</v>
       </c>
       <c r="Q56">
-        <v>-36.66557817333333</v>
+        <v>-37.61200863333333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1551934855108354</v>
+        <v>0.1576244518555207</v>
       </c>
       <c r="T56">
-        <v>1.0579186124049</v>
+        <v>1.081427914902787</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.06526308896338985</v>
+        <v>0.06407648734587368</v>
       </c>
       <c r="W56">
-        <v>0.2204109636224327</v>
+        <v>0.220690764283843</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2610523558535595</v>
+        <v>0.2563059493834947</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6044,22 +6044,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.192310923691098</v>
+        <v>0.1942109236910979</v>
       </c>
       <c r="C57">
-        <v>-102.801206633344</v>
+        <v>-110.6011911481722</v>
       </c>
       <c r="D57">
-        <v>191.245793366656</v>
+        <v>188.7974088518278</v>
       </c>
       <c r="E57">
-        <v>287.578</v>
+        <v>292.9296</v>
       </c>
       <c r="F57">
-        <v>294.338</v>
+        <v>299.6896</v>
       </c>
       <c r="G57">
         <v>0.291</v>
@@ -6080,37 +6080,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M57">
-        <v>69.4049004</v>
+        <v>70.66680768000001</v>
       </c>
       <c r="N57">
-        <v>-51.61601151111111</v>
+        <v>-52.87791879111111</v>
       </c>
       <c r="O57">
-        <v>-12.90400287777778</v>
+        <v>-13.21947969777778</v>
       </c>
       <c r="P57">
-        <v>-38.71200863333333</v>
+        <v>-39.65843909333334</v>
       </c>
       <c r="Q57">
-        <v>-37.61200863333333</v>
+        <v>-38.55843909333333</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1576244518555207</v>
+        <v>0.1601659166704189</v>
       </c>
       <c r="T57">
-        <v>1.081427914902787</v>
+        <v>1.106005822059668</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.06407648734587368</v>
+        <v>0.0629322643575545</v>
       </c>
       <c r="W57">
-        <v>0.220690764283843</v>
+        <v>0.2209605720644887</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2563059493834947</v>
+        <v>0.251729057430218</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6126,22 +6126,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1942109236910979</v>
+        <v>0.196110923691098</v>
       </c>
       <c r="C58">
-        <v>-110.6011911481722</v>
+        <v>-118.3392782244919</v>
       </c>
       <c r="D58">
-        <v>188.7974088518278</v>
+        <v>186.4109217755081</v>
       </c>
       <c r="E58">
-        <v>292.9296</v>
+        <v>298.2812</v>
       </c>
       <c r="F58">
-        <v>299.6896</v>
+        <v>305.0412</v>
       </c>
       <c r="G58">
         <v>0.291</v>
@@ -6162,37 +6162,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M58">
-        <v>70.66680768000001</v>
+        <v>71.92871496000001</v>
       </c>
       <c r="N58">
-        <v>-52.87791879111111</v>
+        <v>-54.13982607111112</v>
       </c>
       <c r="O58">
-        <v>-13.21947969777778</v>
+        <v>-13.53495651777778</v>
       </c>
       <c r="P58">
-        <v>-39.65843909333334</v>
+        <v>-40.60486955333334</v>
       </c>
       <c r="Q58">
-        <v>-38.55843909333333</v>
+        <v>-39.50486955333334</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1601659166704189</v>
+        <v>0.1628255891511263</v>
       </c>
       <c r="T58">
-        <v>1.106005822059668</v>
+        <v>1.131726887688963</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.0629322643575545</v>
+        <v>0.06182818954426407</v>
       </c>
       <c r="W58">
-        <v>0.2209605720644887</v>
+        <v>0.2212209129054626</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.251729057430218</v>
+        <v>0.2473127581770562</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6208,22 +6208,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.196110923691098</v>
+        <v>0.198010923691098</v>
       </c>
       <c r="C59">
-        <v>-118.3392782244919</v>
+        <v>-126.0177857997475</v>
       </c>
       <c r="D59">
-        <v>186.4109217755081</v>
+        <v>184.0840142002526</v>
       </c>
       <c r="E59">
-        <v>298.2812</v>
+        <v>303.6328</v>
       </c>
       <c r="F59">
-        <v>305.0412</v>
+        <v>310.3928</v>
       </c>
       <c r="G59">
         <v>0.291</v>
@@ -6244,37 +6244,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M59">
-        <v>71.92871496000001</v>
+        <v>73.19062224000001</v>
       </c>
       <c r="N59">
-        <v>-54.13982607111112</v>
+        <v>-55.40173335111112</v>
       </c>
       <c r="O59">
-        <v>-13.53495651777778</v>
+        <v>-13.85043333777778</v>
       </c>
       <c r="P59">
-        <v>-40.60486955333334</v>
+        <v>-41.55130001333334</v>
       </c>
       <c r="Q59">
-        <v>-39.50486955333334</v>
+        <v>-40.45130001333334</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1628255891511263</v>
+        <v>0.1656119127023436</v>
       </c>
       <c r="T59">
-        <v>1.131726887688963</v>
+        <v>1.158672765967272</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.06182818954426407</v>
+        <v>0.06076218627625951</v>
       </c>
       <c r="W59">
-        <v>0.2212209129054626</v>
+        <v>0.221472276476058</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2473127581770562</v>
+        <v>0.243048745105038</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6290,22 +6290,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.198010923691098</v>
+        <v>0.1999109236910979</v>
       </c>
       <c r="C60">
-        <v>-126.0177857997474</v>
+        <v>-133.6389175020007</v>
       </c>
       <c r="D60">
-        <v>184.0840142002526</v>
+        <v>181.8144824979993</v>
       </c>
       <c r="E60">
-        <v>303.6328</v>
+        <v>308.9844</v>
       </c>
       <c r="F60">
-        <v>310.3928</v>
+        <v>315.7444</v>
       </c>
       <c r="G60">
         <v>0.291</v>
@@ -6326,37 +6326,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M60">
-        <v>73.19062224</v>
+        <v>74.45252952</v>
       </c>
       <c r="N60">
-        <v>-55.4017333511111</v>
+        <v>-56.66364063111111</v>
       </c>
       <c r="O60">
-        <v>-13.85043333777778</v>
+        <v>-14.16591015777778</v>
       </c>
       <c r="P60">
-        <v>-41.55130001333333</v>
+        <v>-42.49773047333333</v>
       </c>
       <c r="Q60">
-        <v>-40.45130001333333</v>
+        <v>-41.39773047333333</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1656119127023436</v>
+        <v>0.1685341544755715</v>
       </c>
       <c r="T60">
-        <v>1.158672765967271</v>
+        <v>1.186933077332327</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.06076218627625952</v>
+        <v>0.05973231871225512</v>
       </c>
       <c r="W60">
-        <v>0.221472276476058</v>
+        <v>0.2217151192476502</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.243048745105038</v>
+        <v>0.2389292748490205</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6372,22 +6372,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1999109236910979</v>
+        <v>0.2018109236910979</v>
       </c>
       <c r="C61">
-        <v>-133.6389175020007</v>
+        <v>-141.2047696105913</v>
       </c>
       <c r="D61">
-        <v>181.8144824979993</v>
+        <v>179.6002303894086</v>
       </c>
       <c r="E61">
-        <v>308.9844</v>
+        <v>314.336</v>
       </c>
       <c r="F61">
-        <v>315.7444</v>
+        <v>321.0959999999999</v>
       </c>
       <c r="G61">
         <v>0.291</v>
@@ -6408,37 +6408,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M61">
-        <v>74.45252952</v>
+        <v>75.71443679999999</v>
       </c>
       <c r="N61">
-        <v>-56.66364063111111</v>
+        <v>-57.9255479111111</v>
       </c>
       <c r="O61">
-        <v>-14.16591015777778</v>
+        <v>-14.48138697777777</v>
       </c>
       <c r="P61">
-        <v>-42.49773047333333</v>
+        <v>-43.44416093333332</v>
       </c>
       <c r="Q61">
-        <v>-41.39773047333333</v>
+        <v>-42.34416093333332</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1685341544755715</v>
+        <v>0.1716025083374608</v>
       </c>
       <c r="T61">
-        <v>1.186933077332327</v>
+        <v>1.216606404265635</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.05973231871225512</v>
+        <v>0.05873678006705088</v>
       </c>
       <c r="W61">
-        <v>0.2217151192476502</v>
+        <v>0.2219498672601894</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2389292748490205</v>
+        <v>0.2349471202682035</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6454,22 +6454,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2018109236910979</v>
+        <v>0.203710923691098</v>
       </c>
       <c r="C62">
-        <v>-141.2047696105913</v>
+        <v>-148.7173375142901</v>
       </c>
       <c r="D62">
-        <v>179.6002303894086</v>
+        <v>177.4392624857099</v>
       </c>
       <c r="E62">
-        <v>314.336</v>
+        <v>319.6876</v>
       </c>
       <c r="F62">
-        <v>321.0959999999999</v>
+        <v>326.4476</v>
       </c>
       <c r="G62">
         <v>0.291</v>
@@ -6490,37 +6490,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M62">
-        <v>75.71443679999999</v>
+        <v>76.97634407999999</v>
       </c>
       <c r="N62">
-        <v>-57.9255479111111</v>
+        <v>-59.1874551911111</v>
       </c>
       <c r="O62">
-        <v>-14.48138697777777</v>
+        <v>-14.79686379777777</v>
       </c>
       <c r="P62">
-        <v>-43.44416093333332</v>
+        <v>-44.39059139333332</v>
       </c>
       <c r="Q62">
-        <v>-42.34416093333332</v>
+        <v>-43.29059139333332</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1716025083374608</v>
+        <v>0.174828213679447</v>
       </c>
       <c r="T62">
-        <v>1.216606404265635</v>
+        <v>1.247801440272446</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.05873678006705088</v>
+        <v>0.0577738820331648</v>
       </c>
       <c r="W62">
-        <v>0.2219498672601894</v>
+        <v>0.2221769186165798</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2349471202682035</v>
+        <v>0.2310955281326592</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6536,22 +6536,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.203710923691098</v>
+        <v>0.205610923691098</v>
       </c>
       <c r="C63">
-        <v>-148.7173375142901</v>
+        <v>-156.178521708763</v>
       </c>
       <c r="D63">
-        <v>177.4392624857099</v>
+        <v>175.329678291237</v>
       </c>
       <c r="E63">
-        <v>319.6876</v>
+        <v>325.0392</v>
       </c>
       <c r="F63">
-        <v>326.4476</v>
+        <v>331.7992</v>
       </c>
       <c r="G63">
         <v>0.291</v>
@@ -6572,37 +6572,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M63">
-        <v>76.97634407999999</v>
+        <v>78.23825136000001</v>
       </c>
       <c r="N63">
-        <v>-59.1874551911111</v>
+        <v>-60.44936247111112</v>
       </c>
       <c r="O63">
-        <v>-14.79686379777777</v>
+        <v>-15.11234061777778</v>
       </c>
       <c r="P63">
-        <v>-44.39059139333332</v>
+        <v>-45.33702185333334</v>
       </c>
       <c r="Q63">
-        <v>-43.29059139333332</v>
+        <v>-44.23702185333334</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.174828213679447</v>
+        <v>0.1782236929868008</v>
       </c>
       <c r="T63">
-        <v>1.247801440272446</v>
+        <v>1.280638320279616</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.0577738820331648</v>
+        <v>0.05684204522617826</v>
       </c>
       <c r="W63">
-        <v>0.2221769186165798</v>
+        <v>0.2223966457356672</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2310955281326592</v>
+        <v>0.227368180904713</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6618,22 +6618,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.205610923691098</v>
+        <v>0.2075109236910979</v>
       </c>
       <c r="C64">
-        <v>-156.178521708763</v>
+        <v>-163.5901333712384</v>
       </c>
       <c r="D64">
-        <v>175.329678291237</v>
+        <v>173.2696666287616</v>
       </c>
       <c r="E64">
-        <v>325.0392</v>
+        <v>330.3908</v>
       </c>
       <c r="F64">
-        <v>331.7992</v>
+        <v>337.1508</v>
       </c>
       <c r="G64">
         <v>0.291</v>
@@ -6654,37 +6654,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M64">
-        <v>78.23825136000001</v>
+        <v>79.50015864000001</v>
       </c>
       <c r="N64">
-        <v>-60.44936247111112</v>
+        <v>-61.71126975111112</v>
       </c>
       <c r="O64">
-        <v>-15.11234061777778</v>
+        <v>-15.42781743777778</v>
       </c>
       <c r="P64">
-        <v>-45.33702185333334</v>
+        <v>-46.28345231333334</v>
       </c>
       <c r="Q64">
-        <v>-44.23702185333334</v>
+        <v>-45.18345231333334</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1782236929868008</v>
+        <v>0.1818027117161738</v>
       </c>
       <c r="T64">
-        <v>1.280638320279616</v>
+        <v>1.315250166773659</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05684204522617826</v>
+        <v>0.05593979054004844</v>
       </c>
       <c r="W64">
-        <v>0.2223966457356672</v>
+        <v>0.2226093973906566</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.227368180904713</v>
+        <v>0.2237591621601938</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6700,22 +6700,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2075109236910979</v>
+        <v>0.209410923691098</v>
       </c>
       <c r="C65">
-        <v>-163.5901333712384</v>
+        <v>-170.9538995467452</v>
       </c>
       <c r="D65">
-        <v>173.2696666287616</v>
+        <v>171.2575004532547</v>
       </c>
       <c r="E65">
-        <v>330.3908</v>
+        <v>335.7424</v>
       </c>
       <c r="F65">
-        <v>337.1508</v>
+        <v>342.5024</v>
       </c>
       <c r="G65">
         <v>0.291</v>
@@ -6736,37 +6736,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M65">
-        <v>79.50015864000001</v>
+        <v>80.76206592</v>
       </c>
       <c r="N65">
-        <v>-61.71126975111112</v>
+        <v>-62.97317703111111</v>
       </c>
       <c r="O65">
-        <v>-15.42781743777778</v>
+        <v>-15.74329425777778</v>
       </c>
       <c r="P65">
-        <v>-46.28345231333334</v>
+        <v>-47.22988277333333</v>
       </c>
       <c r="Q65">
-        <v>-45.18345231333334</v>
+        <v>-46.12988277333333</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1818027117161738</v>
+        <v>0.1855805648194009</v>
       </c>
       <c r="T65">
-        <v>1.315250166773659</v>
+        <v>1.351784893628484</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05593979054004844</v>
+        <v>0.05506573131286019</v>
       </c>
       <c r="W65">
-        <v>0.2226093973906566</v>
+        <v>0.2228155005564276</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2237591621601938</v>
+        <v>0.2202629252514408</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6782,22 +6782,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.209410923691098</v>
+        <v>0.211310923691098</v>
       </c>
       <c r="C66">
-        <v>-170.9538995467452</v>
+        <v>-178.2714679771341</v>
       </c>
       <c r="D66">
-        <v>171.2575004532547</v>
+        <v>169.2915320228659</v>
       </c>
       <c r="E66">
-        <v>335.7424</v>
+        <v>341.094</v>
       </c>
       <c r="F66">
-        <v>342.5024</v>
+        <v>347.854</v>
       </c>
       <c r="G66">
         <v>0.291</v>
@@ -6818,37 +6818,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M66">
-        <v>80.76206592</v>
+        <v>82.0239732</v>
       </c>
       <c r="N66">
-        <v>-62.97317703111111</v>
+        <v>-64.23508431111111</v>
       </c>
       <c r="O66">
-        <v>-15.74329425777778</v>
+        <v>-16.05877107777778</v>
       </c>
       <c r="P66">
-        <v>-47.22988277333333</v>
+        <v>-48.17631323333333</v>
       </c>
       <c r="Q66">
-        <v>-46.12988277333333</v>
+        <v>-47.07631323333333</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1855805648194009</v>
+        <v>0.1895742952428124</v>
       </c>
       <c r="T66">
-        <v>1.351784893628484</v>
+        <v>1.390407319160726</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05506573131286019</v>
+        <v>0.05421856621573926</v>
       </c>
       <c r="W66">
-        <v>0.2228155005564276</v>
+        <v>0.2230152620863287</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2202629252514408</v>
+        <v>0.216874264862957</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6864,22 +6864,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.211310923691098</v>
+        <v>0.213210923691098</v>
       </c>
       <c r="C67">
-        <v>-178.2714679771341</v>
+        <v>-185.5444116012631</v>
       </c>
       <c r="D67">
-        <v>169.2915320228659</v>
+        <v>167.3701883987369</v>
       </c>
       <c r="E67">
-        <v>341.094</v>
+        <v>346.4456</v>
       </c>
       <c r="F67">
-        <v>347.854</v>
+        <v>353.2056</v>
       </c>
       <c r="G67">
         <v>0.291</v>
@@ -6900,37 +6900,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M67">
-        <v>82.0239732</v>
+        <v>83.28588048</v>
       </c>
       <c r="N67">
-        <v>-64.23508431111111</v>
+        <v>-65.49699159111111</v>
       </c>
       <c r="O67">
-        <v>-16.05877107777778</v>
+        <v>-16.37424789777778</v>
       </c>
       <c r="P67">
-        <v>-48.17631323333333</v>
+        <v>-49.12274369333333</v>
       </c>
       <c r="Q67">
-        <v>-47.07631323333333</v>
+        <v>-48.02274369333333</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1895742952428124</v>
+        <v>0.193802950985248</v>
       </c>
       <c r="T67">
-        <v>1.390407319160726</v>
+        <v>1.431301652077218</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05421856621573926</v>
+        <v>0.05339707278822806</v>
       </c>
       <c r="W67">
-        <v>0.2230152620863287</v>
+        <v>0.2232089702365359</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.216874264862957</v>
+        <v>0.2135882911529122</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6946,22 +6946,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.213210923691098</v>
+        <v>0.215110923691098</v>
       </c>
       <c r="C68">
-        <v>-185.5444116012631</v>
+        <v>-192.7742327521783</v>
       </c>
       <c r="D68">
-        <v>167.3701883987369</v>
+        <v>165.4919672478217</v>
       </c>
       <c r="E68">
-        <v>346.4456</v>
+        <v>351.7972</v>
       </c>
       <c r="F68">
-        <v>353.2056</v>
+        <v>358.5572</v>
       </c>
       <c r="G68">
         <v>0.291</v>
@@ -6982,37 +6982,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M68">
-        <v>83.28588048</v>
+        <v>84.54778776000001</v>
       </c>
       <c r="N68">
-        <v>-65.49699159111111</v>
+        <v>-66.75889887111111</v>
       </c>
       <c r="O68">
-        <v>-16.37424789777778</v>
+        <v>-16.68972471777778</v>
       </c>
       <c r="P68">
-        <v>-49.12274369333333</v>
+        <v>-50.06917415333334</v>
       </c>
       <c r="Q68">
-        <v>-48.02274369333333</v>
+        <v>-48.96917415333333</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.193802950985248</v>
+        <v>0.1982878888938919</v>
       </c>
       <c r="T68">
-        <v>1.431301652077218</v>
+        <v>1.474674429412891</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.05339707278822806</v>
+        <v>0.05260010155258286</v>
       </c>
       <c r="W68">
-        <v>0.2232089702365359</v>
+        <v>0.223396896053901</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2135882911529122</v>
+        <v>0.2104004062103315</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7028,22 +7028,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.215110923691098</v>
+        <v>0.217010923691098</v>
       </c>
       <c r="C69">
-        <v>-192.7742327521783</v>
+        <v>-199.9623670748256</v>
       </c>
       <c r="D69">
-        <v>165.4919672478217</v>
+        <v>163.6554329251744</v>
       </c>
       <c r="E69">
-        <v>351.7972</v>
+        <v>357.1488</v>
       </c>
       <c r="F69">
-        <v>358.5572</v>
+        <v>363.9088</v>
       </c>
       <c r="G69">
         <v>0.291</v>
@@ -7064,37 +7064,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M69">
-        <v>84.54778776000001</v>
+        <v>85.80969503999999</v>
       </c>
       <c r="N69">
-        <v>-66.75889887111111</v>
+        <v>-68.0208061511111</v>
       </c>
       <c r="O69">
-        <v>-16.68972471777778</v>
+        <v>-17.00520153777778</v>
       </c>
       <c r="P69">
-        <v>-50.06917415333334</v>
+        <v>-51.01560461333332</v>
       </c>
       <c r="Q69">
-        <v>-48.96917415333333</v>
+        <v>-49.91560461333332</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1982878888938919</v>
+        <v>0.203053135421826</v>
       </c>
       <c r="T69">
-        <v>1.474674429412891</v>
+        <v>1.520758005332044</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05260010155258286</v>
+        <v>0.05182657064739783</v>
       </c>
       <c r="W69">
-        <v>0.223396896053901</v>
+        <v>0.2235792946413436</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2104004062103315</v>
+        <v>0.2073062825895913</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7110,22 +7110,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.217010923691098</v>
+        <v>0.218910923691098</v>
       </c>
       <c r="C70">
-        <v>-199.9623670748256</v>
+        <v>-207.1101871857685</v>
       </c>
       <c r="D70">
-        <v>163.6554329251744</v>
+        <v>161.8592128142315</v>
       </c>
       <c r="E70">
-        <v>357.1488</v>
+        <v>362.5004</v>
       </c>
       <c r="F70">
-        <v>363.9088</v>
+        <v>369.2604</v>
       </c>
       <c r="G70">
         <v>0.291</v>
@@ -7146,37 +7146,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M70">
-        <v>85.80969503999999</v>
+        <v>87.07160232000001</v>
       </c>
       <c r="N70">
-        <v>-68.0208061511111</v>
+        <v>-69.28271343111112</v>
       </c>
       <c r="O70">
-        <v>-17.00520153777778</v>
+        <v>-17.32067835777778</v>
       </c>
       <c r="P70">
-        <v>-51.01560461333332</v>
+        <v>-51.96203507333334</v>
       </c>
       <c r="Q70">
-        <v>-49.91560461333332</v>
+        <v>-50.86203507333334</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.203053135421826</v>
+        <v>0.2081258172096269</v>
       </c>
       <c r="T70">
-        <v>1.520758005332044</v>
+        <v>1.569814715181465</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05182657064739783</v>
+        <v>0.05107546092787032</v>
       </c>
       <c r="W70">
-        <v>0.2235792946413436</v>
+        <v>0.2237564063132082</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2073062825895913</v>
+        <v>0.2043018437114813</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7192,22 +7192,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.218910923691098</v>
+        <v>0.220810923691098</v>
       </c>
       <c r="C71">
-        <v>-207.1101871857685</v>
+        <v>-214.2190060945141</v>
       </c>
       <c r="D71">
-        <v>161.8592128142315</v>
+        <v>160.1019939054859</v>
       </c>
       <c r="E71">
-        <v>362.5004</v>
+        <v>367.852</v>
       </c>
       <c r="F71">
-        <v>369.2604</v>
+        <v>374.612</v>
       </c>
       <c r="G71">
         <v>0.291</v>
@@ -7228,37 +7228,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M71">
-        <v>87.07160232000001</v>
+        <v>88.33350960000001</v>
       </c>
       <c r="N71">
-        <v>-69.28271343111112</v>
+        <v>-70.54462071111112</v>
       </c>
       <c r="O71">
-        <v>-17.32067835777778</v>
+        <v>-17.63615517777778</v>
       </c>
       <c r="P71">
-        <v>-51.96203507333334</v>
+        <v>-52.90846553333334</v>
       </c>
       <c r="Q71">
-        <v>-50.86203507333334</v>
+        <v>-51.80846553333334</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2081258172096269</v>
+        <v>0.2135366777832811</v>
       </c>
       <c r="T71">
-        <v>1.569814715181465</v>
+        <v>1.622141872354181</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05107546092787032</v>
+        <v>0.0503458114860436</v>
       </c>
       <c r="W71">
-        <v>0.2237564063132082</v>
+        <v>0.2239284576515909</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2043018437114813</v>
+        <v>0.2013832459441743</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7274,22 +7274,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.220810923691098</v>
+        <v>0.222710923691098</v>
       </c>
       <c r="C72">
-        <v>-214.2190060945141</v>
+        <v>-221.290080404374</v>
       </c>
       <c r="D72">
-        <v>160.1019939054859</v>
+        <v>158.382519595626</v>
       </c>
       <c r="E72">
-        <v>367.852</v>
+        <v>373.2036000000001</v>
       </c>
       <c r="F72">
-        <v>374.612</v>
+        <v>379.9636</v>
       </c>
       <c r="G72">
         <v>0.291</v>
@@ -7310,37 +7310,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M72">
-        <v>88.33350960000001</v>
+        <v>89.59541688000002</v>
       </c>
       <c r="N72">
-        <v>-70.54462071111112</v>
+        <v>-71.80652799111112</v>
       </c>
       <c r="O72">
-        <v>-17.63615517777778</v>
+        <v>-17.95163199777778</v>
       </c>
       <c r="P72">
-        <v>-52.90846553333334</v>
+        <v>-53.85489599333334</v>
       </c>
       <c r="Q72">
-        <v>-51.80846553333334</v>
+        <v>-52.75489599333334</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2135366777832811</v>
+        <v>0.2193207011551184</v>
       </c>
       <c r="T72">
-        <v>1.622141872354181</v>
+        <v>1.678077798987083</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.0503458114860436</v>
+        <v>0.04963671554962044</v>
       </c>
       <c r="W72">
-        <v>0.2239284576515909</v>
+        <v>0.2240956624733995</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2013832459441743</v>
+        <v>0.1985468621984818</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7356,22 +7356,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.222710923691098</v>
+        <v>0.224610923691098</v>
       </c>
       <c r="C73">
-        <v>-221.2900804043739</v>
+        <v>-228.3246133092536</v>
       </c>
       <c r="D73">
-        <v>158.3825195956261</v>
+        <v>156.6995866907463</v>
       </c>
       <c r="E73">
-        <v>373.2036</v>
+        <v>378.5552</v>
       </c>
       <c r="F73">
-        <v>379.9636</v>
+        <v>385.3151999999999</v>
       </c>
       <c r="G73">
         <v>0.291</v>
@@ -7392,37 +7392,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M73">
-        <v>89.59541688</v>
+        <v>90.85732415999999</v>
       </c>
       <c r="N73">
-        <v>-71.80652799111111</v>
+        <v>-73.0684352711111</v>
       </c>
       <c r="O73">
-        <v>-17.95163199777778</v>
+        <v>-18.26710881777777</v>
       </c>
       <c r="P73">
-        <v>-53.85489599333333</v>
+        <v>-54.80132645333332</v>
       </c>
       <c r="Q73">
-        <v>-52.75489599333333</v>
+        <v>-53.70132645333332</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2193207011551183</v>
+        <v>0.2255178690535154</v>
       </c>
       <c r="T73">
-        <v>1.678077798987083</v>
+        <v>1.738009148950907</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04963671554962045</v>
+        <v>0.0489473167225424</v>
       </c>
       <c r="W73">
-        <v>0.2240956624733995</v>
+        <v>0.2242582227168245</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1985468621984818</v>
+        <v>0.1957892668901696</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7438,22 +7438,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.224610923691098</v>
+        <v>0.226510923691098</v>
       </c>
       <c r="C74">
-        <v>-228.3246133092536</v>
+        <v>-235.3237574013936</v>
       </c>
       <c r="D74">
-        <v>156.6995866907463</v>
+        <v>155.0520425986064</v>
       </c>
       <c r="E74">
-        <v>378.5552</v>
+        <v>383.9068</v>
       </c>
       <c r="F74">
-        <v>385.3151999999999</v>
+        <v>390.6668</v>
       </c>
       <c r="G74">
         <v>0.291</v>
@@ -7474,37 +7474,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M74">
-        <v>90.85732415999999</v>
+        <v>92.11923143999999</v>
       </c>
       <c r="N74">
-        <v>-73.0684352711111</v>
+        <v>-74.3303425511111</v>
       </c>
       <c r="O74">
-        <v>-18.26710881777777</v>
+        <v>-18.58258563777778</v>
       </c>
       <c r="P74">
-        <v>-54.80132645333332</v>
+        <v>-55.74775691333333</v>
       </c>
       <c r="Q74">
-        <v>-53.70132645333332</v>
+        <v>-54.64775691333332</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2255178690535154</v>
+        <v>0.2321740864258678</v>
       </c>
       <c r="T74">
-        <v>1.738009148950907</v>
+        <v>1.802379858171311</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0489473167225424</v>
+        <v>0.04827680553456237</v>
       </c>
       <c r="W74">
-        <v>0.2242582227168245</v>
+        <v>0.2244163292549502</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1957892668901696</v>
+        <v>0.1931072221382495</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7520,22 +7520,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.226510923691098</v>
+        <v>0.228410923691098</v>
       </c>
       <c r="C75">
-        <v>-235.3237574013936</v>
+        <v>-242.288617303828</v>
       </c>
       <c r="D75">
-        <v>155.0520425986064</v>
+        <v>153.438782696172</v>
       </c>
       <c r="E75">
-        <v>383.9068</v>
+        <v>389.2584</v>
       </c>
       <c r="F75">
-        <v>390.6668</v>
+        <v>396.0184</v>
       </c>
       <c r="G75">
         <v>0.291</v>
@@ -7556,37 +7556,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M75">
-        <v>92.11923143999999</v>
+        <v>93.38113872</v>
       </c>
       <c r="N75">
-        <v>-74.3303425511111</v>
+        <v>-75.5922498311111</v>
       </c>
       <c r="O75">
-        <v>-18.58258563777778</v>
+        <v>-18.89806245777778</v>
       </c>
       <c r="P75">
-        <v>-55.74775691333333</v>
+        <v>-56.69418737333333</v>
       </c>
       <c r="Q75">
-        <v>-54.64775691333332</v>
+        <v>-55.59418737333333</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2321740864258678</v>
+        <v>0.2393423205191705</v>
       </c>
       <c r="T75">
-        <v>1.802379858171311</v>
+        <v>1.871702160408669</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04827680553456237</v>
+        <v>0.04762441627058179</v>
       </c>
       <c r="W75">
-        <v>0.2244163292549502</v>
+        <v>0.2245701626433968</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1931072221382495</v>
+        <v>0.1904976650823271</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7602,22 +7602,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.228410923691098</v>
+        <v>0.230310923691098</v>
       </c>
       <c r="C76">
-        <v>-242.288617303828</v>
+        <v>-249.2202521401979</v>
       </c>
       <c r="D76">
-        <v>153.438782696172</v>
+        <v>151.8587478598021</v>
       </c>
       <c r="E76">
-        <v>389.2584</v>
+        <v>394.61</v>
       </c>
       <c r="F76">
-        <v>396.0184</v>
+        <v>401.37</v>
       </c>
       <c r="G76">
         <v>0.291</v>
@@ -7638,37 +7638,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M76">
-        <v>93.38113872</v>
+        <v>94.643046</v>
       </c>
       <c r="N76">
-        <v>-75.5922498311111</v>
+        <v>-76.85415711111111</v>
       </c>
       <c r="O76">
-        <v>-18.89806245777778</v>
+        <v>-19.21353927777778</v>
       </c>
       <c r="P76">
-        <v>-56.69418737333333</v>
+        <v>-57.64061783333333</v>
       </c>
       <c r="Q76">
-        <v>-55.59418737333333</v>
+        <v>-56.54061783333333</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2393423205191705</v>
+        <v>0.2470840133399372</v>
       </c>
       <c r="T76">
-        <v>1.871702160408669</v>
+        <v>1.946570246825016</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04762441627058179</v>
+        <v>0.0469894240536407</v>
       </c>
       <c r="W76">
-        <v>0.2245701626433968</v>
+        <v>0.2247198938081515</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1904976650823271</v>
+        <v>0.1879576962145628</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7684,22 +7684,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.230310923691098</v>
+        <v>0.232210923691098</v>
       </c>
       <c r="C77">
-        <v>-249.2202521401979</v>
+        <v>-256.1196778535222</v>
       </c>
       <c r="D77">
-        <v>151.8587478598021</v>
+        <v>150.3109221464778</v>
       </c>
       <c r="E77">
-        <v>394.61</v>
+        <v>399.9616</v>
       </c>
       <c r="F77">
-        <v>401.37</v>
+        <v>406.7216</v>
       </c>
       <c r="G77">
         <v>0.291</v>
@@ -7720,37 +7720,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M77">
-        <v>94.643046</v>
+        <v>95.90495328</v>
       </c>
       <c r="N77">
-        <v>-76.85415711111111</v>
+        <v>-78.11606439111111</v>
       </c>
       <c r="O77">
-        <v>-19.21353927777778</v>
+        <v>-19.52901609777778</v>
       </c>
       <c r="P77">
-        <v>-57.64061783333333</v>
+        <v>-58.58704829333333</v>
       </c>
       <c r="Q77">
-        <v>-56.54061783333333</v>
+        <v>-57.48704829333333</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2470840133399372</v>
+        <v>0.2554708472291013</v>
       </c>
       <c r="T77">
-        <v>1.946570246825016</v>
+        <v>2.027677340442725</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0469894240536407</v>
+        <v>0.04637114215819806</v>
       </c>
       <c r="W77">
-        <v>0.2247198938081515</v>
+        <v>0.2248656846790969</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1879576962145628</v>
+        <v>0.1854845686327922</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7766,22 +7766,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.232210923691098</v>
+        <v>0.234110923691098</v>
       </c>
       <c r="C78">
-        <v>-256.1196778535222</v>
+        <v>-262.9878693845944</v>
       </c>
       <c r="D78">
-        <v>150.3109221464778</v>
+        <v>148.7943306154056</v>
       </c>
       <c r="E78">
-        <v>399.9616</v>
+        <v>405.3132</v>
       </c>
       <c r="F78">
-        <v>406.7216</v>
+        <v>412.0732</v>
       </c>
       <c r="G78">
         <v>0.291</v>
@@ -7802,37 +7802,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M78">
-        <v>95.90495328</v>
+        <v>97.16686056</v>
       </c>
       <c r="N78">
-        <v>-78.11606439111111</v>
+        <v>-79.37797167111111</v>
       </c>
       <c r="O78">
-        <v>-19.52901609777778</v>
+        <v>-19.84449291777778</v>
       </c>
       <c r="P78">
-        <v>-58.58704829333333</v>
+        <v>-59.53347875333333</v>
       </c>
       <c r="Q78">
-        <v>-57.48704829333333</v>
+        <v>-58.43347875333333</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2554708472291013</v>
+        <v>0.2645869710216709</v>
       </c>
       <c r="T78">
-        <v>2.027677340442725</v>
+        <v>2.1158372248098</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04637114215819806</v>
+        <v>0.04576891953276691</v>
       </c>
       <c r="W78">
-        <v>0.2248656846790969</v>
+        <v>0.2250076887741736</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1854845686327922</v>
+        <v>0.1830756781310676</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7848,22 +7848,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.234110923691098</v>
+        <v>0.2360109236910979</v>
       </c>
       <c r="C79">
-        <v>-262.9878693845944</v>
+        <v>-269.8257627198205</v>
       </c>
       <c r="D79">
-        <v>148.7943306154056</v>
+        <v>147.3080372801795</v>
       </c>
       <c r="E79">
-        <v>405.3132</v>
+        <v>410.6648</v>
       </c>
       <c r="F79">
-        <v>412.0732</v>
+        <v>417.4248</v>
       </c>
       <c r="G79">
         <v>0.291</v>
@@ -7884,37 +7884,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M79">
-        <v>97.16686056</v>
+        <v>98.42876784000001</v>
       </c>
       <c r="N79">
-        <v>-79.37797167111111</v>
+        <v>-80.63987895111111</v>
       </c>
       <c r="O79">
-        <v>-19.84449291777778</v>
+        <v>-20.15996973777778</v>
       </c>
       <c r="P79">
-        <v>-59.53347875333333</v>
+        <v>-60.47990921333334</v>
       </c>
       <c r="Q79">
-        <v>-58.43347875333333</v>
+        <v>-59.37990921333333</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2645869710216709</v>
+        <v>0.2745318333408377</v>
       </c>
       <c r="T79">
-        <v>2.1158372248098</v>
+        <v>2.212011644119336</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04576891953276691</v>
+        <v>0.04518213851311605</v>
       </c>
       <c r="W79">
-        <v>0.2250076887741736</v>
+        <v>0.2251460517386072</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1830756781310676</v>
+        <v>0.1807285540524642</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7930,22 +7930,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2360109236910979</v>
+        <v>0.237910923691098</v>
       </c>
       <c r="C80">
-        <v>-269.8257627198205</v>
+        <v>-276.6342568175365</v>
       </c>
       <c r="D80">
-        <v>147.3080372801795</v>
+        <v>145.8511431824634</v>
       </c>
       <c r="E80">
-        <v>410.6648</v>
+        <v>416.0164</v>
       </c>
       <c r="F80">
-        <v>417.4248</v>
+        <v>422.7764</v>
       </c>
       <c r="G80">
         <v>0.291</v>
@@ -7966,37 +7966,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M80">
-        <v>98.42876784000001</v>
+        <v>99.69067511999999</v>
       </c>
       <c r="N80">
-        <v>-80.63987895111111</v>
+        <v>-81.9017862311111</v>
       </c>
       <c r="O80">
-        <v>-20.15996973777778</v>
+        <v>-20.47544655777778</v>
       </c>
       <c r="P80">
-        <v>-60.47990921333334</v>
+        <v>-61.42633967333333</v>
       </c>
       <c r="Q80">
-        <v>-59.37990921333333</v>
+        <v>-60.32633967333333</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2745318333408377</v>
+        <v>0.2854238254046872</v>
       </c>
       <c r="T80">
-        <v>2.212011644119336</v>
+        <v>2.317345531934543</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04518213851311605</v>
+        <v>0.04461021270915256</v>
       </c>
       <c r="W80">
-        <v>0.2251460517386072</v>
+        <v>0.2252809118431818</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1807285540524642</v>
+        <v>0.1784408508366102</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8012,22 +8012,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.237910923691098</v>
+        <v>0.2398109236910979</v>
       </c>
       <c r="C81">
-        <v>-276.6342568175365</v>
+        <v>-283.4142154211371</v>
       </c>
       <c r="D81">
-        <v>145.8511431824634</v>
+        <v>144.4227845788629</v>
       </c>
       <c r="E81">
-        <v>416.0164</v>
+        <v>421.368</v>
       </c>
       <c r="F81">
-        <v>422.7764</v>
+        <v>428.128</v>
       </c>
       <c r="G81">
         <v>0.291</v>
@@ -8048,37 +8048,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M81">
-        <v>99.69067511999999</v>
+        <v>100.9525824</v>
       </c>
       <c r="N81">
-        <v>-81.9017862311111</v>
+        <v>-83.16369351111111</v>
       </c>
       <c r="O81">
-        <v>-20.47544655777778</v>
+        <v>-20.79092337777778</v>
       </c>
       <c r="P81">
-        <v>-61.42633967333333</v>
+        <v>-62.37277013333333</v>
       </c>
       <c r="Q81">
-        <v>-60.32633967333333</v>
+        <v>-61.27277013333333</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2854238254046872</v>
+        <v>0.2974050166749216</v>
       </c>
       <c r="T81">
-        <v>2.317345531934543</v>
+        <v>2.433212808531271</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04461021270915256</v>
+        <v>0.04405258505028815</v>
       </c>
       <c r="W81">
-        <v>0.2252809118431818</v>
+        <v>0.225412400445142</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1784408508366102</v>
+        <v>0.1762103402011526</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8094,22 +8094,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2398109236910979</v>
+        <v>0.241710923691098</v>
       </c>
       <c r="C82">
-        <v>-283.4142154211371</v>
+        <v>-290.166468766698</v>
       </c>
       <c r="D82">
-        <v>144.4227845788629</v>
+        <v>143.022131233302</v>
       </c>
       <c r="E82">
-        <v>421.368</v>
+        <v>426.7196</v>
       </c>
       <c r="F82">
-        <v>428.128</v>
+        <v>433.4796</v>
       </c>
       <c r="G82">
         <v>0.291</v>
@@ -8130,37 +8130,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M82">
-        <v>100.9525824</v>
+        <v>102.21448968</v>
       </c>
       <c r="N82">
-        <v>-83.16369351111111</v>
+        <v>-84.42560079111111</v>
       </c>
       <c r="O82">
-        <v>-20.79092337777778</v>
+        <v>-21.10640019777778</v>
       </c>
       <c r="P82">
-        <v>-62.37277013333333</v>
+        <v>-63.31920059333333</v>
       </c>
       <c r="Q82">
-        <v>-61.27277013333333</v>
+        <v>-62.21920059333333</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2974050166749216</v>
+        <v>0.3106473859736018</v>
       </c>
       <c r="T82">
-        <v>2.433212808531271</v>
+        <v>2.561276640559233</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04405258505028815</v>
+        <v>0.04350872597559324</v>
       </c>
       <c r="W82">
-        <v>0.225412400445142</v>
+        <v>0.2255406424149551</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1762103402011526</v>
+        <v>0.174034903902373</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8176,22 +8176,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.241710923691098</v>
+        <v>0.243610923691098</v>
       </c>
       <c r="C83">
-        <v>-290.166468766698</v>
+        <v>-296.8918151921868</v>
       </c>
       <c r="D83">
-        <v>143.022131233302</v>
+        <v>141.6483848078132</v>
       </c>
       <c r="E83">
-        <v>426.7196</v>
+        <v>432.0712</v>
       </c>
       <c r="F83">
-        <v>433.4796</v>
+        <v>438.8312</v>
       </c>
       <c r="G83">
         <v>0.291</v>
@@ -8212,37 +8212,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M83">
-        <v>102.21448968</v>
+        <v>103.47639696</v>
       </c>
       <c r="N83">
-        <v>-84.42560079111111</v>
+        <v>-85.68750807111113</v>
       </c>
       <c r="O83">
-        <v>-21.10640019777778</v>
+        <v>-21.42187701777778</v>
       </c>
       <c r="P83">
-        <v>-63.31920059333333</v>
+        <v>-64.26563105333335</v>
       </c>
       <c r="Q83">
-        <v>-62.21920059333333</v>
+        <v>-63.16563105333335</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3106473859736018</v>
+        <v>0.3253611296388019</v>
       </c>
       <c r="T83">
-        <v>2.561276640559233</v>
+        <v>2.703569787256968</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04350872597559324</v>
+        <v>0.04297813175637868</v>
       </c>
       <c r="W83">
-        <v>0.2255406424149551</v>
+        <v>0.2256657565318459</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.174034903902373</v>
+        <v>0.1719125270255147</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8258,22 +8258,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.243610923691098</v>
+        <v>0.245510923691098</v>
       </c>
       <c r="C84">
-        <v>-296.8918151921868</v>
+        <v>-303.5910226548167</v>
       </c>
       <c r="D84">
-        <v>141.6483848078132</v>
+        <v>140.3007773451833</v>
       </c>
       <c r="E84">
-        <v>432.0712</v>
+        <v>437.4228</v>
       </c>
       <c r="F84">
-        <v>438.8312</v>
+        <v>444.1828</v>
       </c>
       <c r="G84">
         <v>0.291</v>
@@ -8294,37 +8294,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M84">
-        <v>103.47639696</v>
+        <v>104.73830424</v>
       </c>
       <c r="N84">
-        <v>-85.68750807111113</v>
+        <v>-86.94941535111111</v>
       </c>
       <c r="O84">
-        <v>-21.42187701777778</v>
+        <v>-21.73735383777778</v>
       </c>
       <c r="P84">
-        <v>-64.26563105333335</v>
+        <v>-65.21206151333334</v>
       </c>
       <c r="Q84">
-        <v>-63.16563105333335</v>
+        <v>-64.11206151333334</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3253611296388019</v>
+        <v>0.341805901970496</v>
       </c>
       <c r="T84">
-        <v>2.703569787256968</v>
+        <v>2.862603304154436</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04297813175637868</v>
+        <v>0.04246032294003677</v>
       </c>
       <c r="W84">
-        <v>0.2256657565318459</v>
+        <v>0.2257878558507393</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1719125270255147</v>
+        <v>0.1698412917601471</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8340,22 +8340,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.245510923691098</v>
+        <v>0.247410923691098</v>
       </c>
       <c r="C85">
-        <v>-303.5910226548167</v>
+        <v>-310.2648301626018</v>
       </c>
       <c r="D85">
-        <v>140.3007773451833</v>
+        <v>138.9785698373983</v>
       </c>
       <c r="E85">
-        <v>437.4228</v>
+        <v>442.7744</v>
       </c>
       <c r="F85">
-        <v>444.1828</v>
+        <v>449.5344</v>
       </c>
       <c r="G85">
         <v>0.291</v>
@@ -8376,37 +8376,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M85">
-        <v>104.73830424</v>
+        <v>106.00021152</v>
       </c>
       <c r="N85">
-        <v>-86.94941535111111</v>
+        <v>-88.21132263111112</v>
       </c>
       <c r="O85">
-        <v>-21.73735383777778</v>
+        <v>-22.05283065777778</v>
       </c>
       <c r="P85">
-        <v>-65.21206151333334</v>
+        <v>-66.15849197333334</v>
       </c>
       <c r="Q85">
-        <v>-64.11206151333334</v>
+        <v>-65.05849197333335</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.341805901970496</v>
+        <v>0.3603062708436521</v>
       </c>
       <c r="T85">
-        <v>2.862603304154436</v>
+        <v>3.04151601066409</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04246032294003677</v>
+        <v>0.04195484290503633</v>
       </c>
       <c r="W85">
-        <v>0.2257878558507393</v>
+        <v>0.2259070480429924</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1698412917601471</v>
+        <v>0.1678193716201454</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8422,22 +8422,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.247410923691098</v>
+        <v>0.249310923691098</v>
       </c>
       <c r="C86">
-        <v>-310.2648301626017</v>
+        <v>-316.9139491257206</v>
       </c>
       <c r="D86">
-        <v>138.9785698373983</v>
+        <v>137.6810508742793</v>
       </c>
       <c r="E86">
-        <v>442.7744</v>
+        <v>448.126</v>
       </c>
       <c r="F86">
-        <v>449.5343999999999</v>
+        <v>454.886</v>
       </c>
       <c r="G86">
         <v>0.291</v>
@@ -8458,37 +8458,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M86">
-        <v>106.00021152</v>
+        <v>107.2621188</v>
       </c>
       <c r="N86">
-        <v>-88.2113226311111</v>
+        <v>-89.4732299111111</v>
       </c>
       <c r="O86">
-        <v>-22.05283065777778</v>
+        <v>-22.36830747777778</v>
       </c>
       <c r="P86">
-        <v>-66.15849197333333</v>
+        <v>-67.10492243333333</v>
       </c>
       <c r="Q86">
-        <v>-65.05849197333333</v>
+        <v>-66.00492243333333</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3603062708436519</v>
+        <v>0.3812733555665621</v>
       </c>
       <c r="T86">
-        <v>3.041516010664087</v>
+        <v>3.24428374470836</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04195484290503634</v>
+        <v>0.04146125651791827</v>
       </c>
       <c r="W86">
-        <v>0.2259070480429924</v>
+        <v>0.2260234357130749</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1678193716201454</v>
+        <v>0.1658450260716731</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8504,22 +8504,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.249310923691098</v>
+        <v>0.2512109236910979</v>
       </c>
       <c r="C87">
-        <v>-316.9139491257206</v>
+        <v>-323.5390646328829</v>
       </c>
       <c r="D87">
-        <v>137.6810508742793</v>
+        <v>136.4075353671171</v>
       </c>
       <c r="E87">
-        <v>448.126</v>
+        <v>453.4776</v>
       </c>
       <c r="F87">
-        <v>454.886</v>
+        <v>460.2376</v>
       </c>
       <c r="G87">
         <v>0.291</v>
@@ -8540,37 +8540,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M87">
-        <v>107.2621188</v>
+        <v>108.52402608</v>
       </c>
       <c r="N87">
-        <v>-89.4732299111111</v>
+        <v>-90.73513719111111</v>
       </c>
       <c r="O87">
-        <v>-22.36830747777778</v>
+        <v>-22.68378429777778</v>
       </c>
       <c r="P87">
-        <v>-67.10492243333333</v>
+        <v>-68.05135289333333</v>
       </c>
       <c r="Q87">
-        <v>-66.00492243333333</v>
+        <v>-66.95135289333334</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3812733555665621</v>
+        <v>0.4052357381070308</v>
       </c>
       <c r="T87">
-        <v>3.24428374470836</v>
+        <v>3.476018297901814</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04146125651791827</v>
+        <v>0.04097914888398898</v>
       </c>
       <c r="W87">
-        <v>0.2260234357130749</v>
+        <v>0.2261371166931554</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1658450260716731</v>
+        <v>0.1639165955359559</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8586,22 +8586,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2512109236910979</v>
+        <v>0.2531109236910979</v>
       </c>
       <c r="C88">
-        <v>-323.5390646328829</v>
+        <v>-330.1408366575066</v>
       </c>
       <c r="D88">
-        <v>136.4075353671171</v>
+        <v>135.1573633424933</v>
       </c>
       <c r="E88">
-        <v>453.4776</v>
+        <v>458.8292</v>
       </c>
       <c r="F88">
-        <v>460.2376</v>
+        <v>465.5891999999999</v>
       </c>
       <c r="G88">
         <v>0.291</v>
@@ -8622,37 +8622,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M88">
-        <v>108.52402608</v>
+        <v>109.78593336</v>
       </c>
       <c r="N88">
-        <v>-90.73513719111111</v>
+        <v>-91.9970444711111</v>
       </c>
       <c r="O88">
-        <v>-22.68378429777778</v>
+        <v>-22.99926111777777</v>
       </c>
       <c r="P88">
-        <v>-68.05135289333333</v>
+        <v>-68.99778335333332</v>
       </c>
       <c r="Q88">
-        <v>-66.95135289333334</v>
+        <v>-67.89778335333332</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4052357381070308</v>
+        <v>0.4328846410383408</v>
       </c>
       <c r="T88">
-        <v>3.476018297901814</v>
+        <v>3.743404320817338</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04097914888398898</v>
+        <v>0.04050812418417302</v>
       </c>
       <c r="W88">
-        <v>0.2261371166931554</v>
+        <v>0.226248184317372</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1639165955359559</v>
+        <v>0.1620324967366921</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8668,22 +8668,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2531109236910979</v>
+        <v>0.255010923691098</v>
       </c>
       <c r="C89">
-        <v>-330.1408366575066</v>
+        <v>-336.7199011981724</v>
       </c>
       <c r="D89">
-        <v>135.1573633424933</v>
+        <v>133.9298988018276</v>
       </c>
       <c r="E89">
-        <v>458.8292</v>
+        <v>464.1808</v>
       </c>
       <c r="F89">
-        <v>465.5891999999999</v>
+        <v>470.9408</v>
       </c>
       <c r="G89">
         <v>0.291</v>
@@ -8704,37 +8704,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M89">
-        <v>109.78593336</v>
+        <v>111.04784064</v>
       </c>
       <c r="N89">
-        <v>-91.9970444711111</v>
+        <v>-93.2589517511111</v>
       </c>
       <c r="O89">
-        <v>-22.99926111777777</v>
+        <v>-23.31473793777777</v>
       </c>
       <c r="P89">
-        <v>-68.99778335333332</v>
+        <v>-69.94421381333332</v>
       </c>
       <c r="Q89">
-        <v>-67.89778335333332</v>
+        <v>-68.84421381333333</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4328846410383408</v>
+        <v>0.4651416944582026</v>
       </c>
       <c r="T89">
-        <v>3.743404320817338</v>
+        <v>4.055354680885451</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04050812418417302</v>
+        <v>0.04004780459117105</v>
       </c>
       <c r="W89">
-        <v>0.226248184317372</v>
+        <v>0.2263567276774019</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1620324967366921</v>
+        <v>0.1601912183646842</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8750,22 +8750,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.255010923691098</v>
+        <v>0.256910923691098</v>
       </c>
       <c r="C90">
-        <v>-336.7199011981724</v>
+        <v>-343.2768713574911</v>
       </c>
       <c r="D90">
-        <v>133.9298988018276</v>
+        <v>132.7245286425089</v>
       </c>
       <c r="E90">
-        <v>464.1808</v>
+        <v>469.5324</v>
       </c>
       <c r="F90">
-        <v>470.9408</v>
+        <v>476.2924</v>
       </c>
       <c r="G90">
         <v>0.291</v>
@@ -8786,37 +8786,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M90">
-        <v>111.04784064</v>
+        <v>112.30974792</v>
       </c>
       <c r="N90">
-        <v>-93.2589517511111</v>
+        <v>-94.52085903111112</v>
       </c>
       <c r="O90">
-        <v>-23.31473793777777</v>
+        <v>-23.63021475777778</v>
       </c>
       <c r="P90">
-        <v>-69.94421381333332</v>
+        <v>-70.89064427333334</v>
       </c>
       <c r="Q90">
-        <v>-68.84421381333333</v>
+        <v>-69.79064427333334</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4651416944582026</v>
+        <v>0.5032636666816757</v>
       </c>
       <c r="T90">
-        <v>4.055354680885451</v>
+        <v>4.424023288238674</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04004780459117105</v>
+        <v>0.03959782925868598</v>
       </c>
       <c r="W90">
-        <v>0.2263567276774019</v>
+        <v>0.2264628318608019</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1601912183646842</v>
+        <v>0.158391317034744</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8832,22 +8832,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.256910923691098</v>
+        <v>0.258810923691098</v>
       </c>
       <c r="C91">
-        <v>-343.2768713574911</v>
+        <v>-349.8123383632343</v>
       </c>
       <c r="D91">
-        <v>132.7245286425089</v>
+        <v>131.5406616367657</v>
       </c>
       <c r="E91">
-        <v>469.5324</v>
+        <v>474.884</v>
       </c>
       <c r="F91">
-        <v>476.2924</v>
+        <v>481.644</v>
       </c>
       <c r="G91">
         <v>0.291</v>
@@ -8868,37 +8868,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M91">
-        <v>112.30974792</v>
+        <v>113.5716552</v>
       </c>
       <c r="N91">
-        <v>-94.52085903111112</v>
+        <v>-95.78276631111112</v>
       </c>
       <c r="O91">
-        <v>-23.63021475777778</v>
+        <v>-23.94569157777778</v>
       </c>
       <c r="P91">
-        <v>-70.89064427333334</v>
+        <v>-71.83707473333334</v>
       </c>
       <c r="Q91">
-        <v>-69.79064427333334</v>
+        <v>-70.73707473333334</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5032636666816757</v>
+        <v>0.5490100333498431</v>
       </c>
       <c r="T91">
-        <v>4.424023288238674</v>
+        <v>4.866425617062541</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03959782925868598</v>
+        <v>0.03915785337803391</v>
       </c>
       <c r="W91">
-        <v>0.2264628318608019</v>
+        <v>0.2265665781734596</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.158391317034744</v>
+        <v>0.1566314135121356</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8914,22 +8914,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.258810923691098</v>
+        <v>0.2607109236910979</v>
       </c>
       <c r="C92">
-        <v>-349.8123383632343</v>
+        <v>-356.3268725352966</v>
       </c>
       <c r="D92">
-        <v>131.5406616367657</v>
+        <v>130.3777274647034</v>
       </c>
       <c r="E92">
-        <v>474.884</v>
+        <v>480.2356</v>
       </c>
       <c r="F92">
-        <v>481.644</v>
+        <v>486.9956</v>
       </c>
       <c r="G92">
         <v>0.291</v>
@@ -8950,37 +8950,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M92">
-        <v>113.5716552</v>
+        <v>114.83356248</v>
       </c>
       <c r="N92">
-        <v>-95.78276631111112</v>
+        <v>-97.04467359111111</v>
       </c>
       <c r="O92">
-        <v>-23.94569157777778</v>
+        <v>-24.26116839777778</v>
       </c>
       <c r="P92">
-        <v>-71.83707473333334</v>
+        <v>-72.78350519333333</v>
       </c>
       <c r="Q92">
-        <v>-70.73707473333334</v>
+        <v>-71.68350519333333</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5490100333498431</v>
+        <v>0.6049222592776036</v>
       </c>
       <c r="T92">
-        <v>4.866425617062541</v>
+        <v>5.407139574513935</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03915785337803391</v>
+        <v>0.03872754729695662</v>
       </c>
       <c r="W92">
-        <v>0.2265665781734596</v>
+        <v>0.2266680443473776</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1566314135121356</v>
+        <v>0.1549101891878265</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8996,22 +8996,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2607109236910979</v>
+        <v>0.262610923691098</v>
       </c>
       <c r="C93">
-        <v>-356.3268725352966</v>
+        <v>-362.8210242018163</v>
       </c>
       <c r="D93">
-        <v>130.3777274647034</v>
+        <v>129.2351757981837</v>
       </c>
       <c r="E93">
-        <v>480.2356</v>
+        <v>485.5872</v>
       </c>
       <c r="F93">
-        <v>486.9956</v>
+        <v>492.3472</v>
       </c>
       <c r="G93">
         <v>0.291</v>
@@ -9032,37 +9032,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M93">
-        <v>114.83356248</v>
+        <v>116.09546976</v>
       </c>
       <c r="N93">
-        <v>-97.04467359111111</v>
+        <v>-98.30658087111111</v>
       </c>
       <c r="O93">
-        <v>-24.26116839777778</v>
+        <v>-24.57664521777778</v>
       </c>
       <c r="P93">
-        <v>-72.78350519333333</v>
+        <v>-73.72993565333333</v>
       </c>
       <c r="Q93">
-        <v>-71.68350519333333</v>
+        <v>-72.62993565333333</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6049222592776036</v>
+        <v>0.6748125416873042</v>
       </c>
       <c r="T93">
-        <v>5.407139574513935</v>
+        <v>6.083032021328179</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03872754729695662</v>
+        <v>0.03830659569590274</v>
       </c>
       <c r="W93">
-        <v>0.2266680443473776</v>
+        <v>0.2267673047349061</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1549101891878265</v>
+        <v>0.153226382783611</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9078,22 +9078,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.262610923691098</v>
+        <v>0.264510923691098</v>
       </c>
       <c r="C94">
-        <v>-362.8210242018163</v>
+        <v>-369.2953245675436</v>
       </c>
       <c r="D94">
-        <v>129.2351757981837</v>
+        <v>128.1124754324564</v>
       </c>
       <c r="E94">
-        <v>485.5872</v>
+        <v>490.9388</v>
       </c>
       <c r="F94">
-        <v>492.3472</v>
+        <v>497.6988</v>
       </c>
       <c r="G94">
         <v>0.291</v>
@@ -9114,37 +9114,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M94">
-        <v>116.09546976</v>
+        <v>117.35737704</v>
       </c>
       <c r="N94">
-        <v>-98.30658087111111</v>
+        <v>-99.56848815111111</v>
       </c>
       <c r="O94">
-        <v>-24.57664521777778</v>
+        <v>-24.89212203777778</v>
       </c>
       <c r="P94">
-        <v>-73.72993565333333</v>
+        <v>-74.67636611333333</v>
       </c>
       <c r="Q94">
-        <v>-72.62993565333333</v>
+        <v>-73.57636611333334</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6748125416873042</v>
+        <v>0.7646714762140621</v>
       </c>
       <c r="T94">
-        <v>6.083032021328179</v>
+        <v>6.952036595803635</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03830659569590274</v>
+        <v>0.03789469681745217</v>
       </c>
       <c r="W94">
-        <v>0.2267673047349061</v>
+        <v>0.2268644304904448</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.153226382783611</v>
+        <v>0.1515787872698087</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9160,22 +9160,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.264510923691098</v>
+        <v>0.266410923691098</v>
       </c>
       <c r="C95">
-        <v>-369.2953245675436</v>
+        <v>-375.7502865373367</v>
       </c>
       <c r="D95">
-        <v>128.1124754324564</v>
+        <v>127.0091134626634</v>
       </c>
       <c r="E95">
-        <v>490.9388</v>
+        <v>496.2904</v>
       </c>
       <c r="F95">
-        <v>497.6988</v>
+        <v>503.0504</v>
       </c>
       <c r="G95">
         <v>0.291</v>
@@ -9196,37 +9196,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M95">
-        <v>117.35737704</v>
+        <v>118.61928432</v>
       </c>
       <c r="N95">
-        <v>-99.56848815111111</v>
+        <v>-100.8303954311111</v>
       </c>
       <c r="O95">
-        <v>-24.89212203777778</v>
+        <v>-25.20759885777778</v>
       </c>
       <c r="P95">
-        <v>-74.67636611333333</v>
+        <v>-75.62279657333333</v>
       </c>
       <c r="Q95">
-        <v>-73.57636611333334</v>
+        <v>-74.52279657333334</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7646714762140621</v>
+        <v>0.884483388916406</v>
       </c>
       <c r="T95">
-        <v>6.952036595803635</v>
+        <v>8.110709361770908</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03789469681745217</v>
+        <v>0.03749156174492609</v>
       </c>
       <c r="W95">
-        <v>0.2268644304904448</v>
+        <v>0.2269594897405464</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1515787872698087</v>
+        <v>0.1499662469797043</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9242,22 +9242,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.266410923691098</v>
+        <v>0.268310923691098</v>
       </c>
       <c r="C96">
-        <v>-375.7502865373367</v>
+        <v>-382.1864054974668</v>
       </c>
       <c r="D96">
-        <v>127.0091134626634</v>
+        <v>125.9245945025332</v>
       </c>
       <c r="E96">
-        <v>496.2904</v>
+        <v>501.642</v>
       </c>
       <c r="F96">
-        <v>503.0504</v>
+        <v>508.402</v>
       </c>
       <c r="G96">
         <v>0.291</v>
@@ -9278,37 +9278,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M96">
-        <v>118.61928432</v>
+        <v>119.8811916</v>
       </c>
       <c r="N96">
-        <v>-100.8303954311111</v>
+        <v>-102.0923027111111</v>
       </c>
       <c r="O96">
-        <v>-25.20759885777778</v>
+        <v>-25.52307567777778</v>
       </c>
       <c r="P96">
-        <v>-75.62279657333333</v>
+        <v>-76.56922703333333</v>
       </c>
       <c r="Q96">
-        <v>-74.52279657333334</v>
+        <v>-75.46922703333334</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.884483388916406</v>
+        <v>1.052220066699688</v>
       </c>
       <c r="T96">
-        <v>8.110709361770908</v>
+        <v>9.732851234125095</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03749156174492609</v>
+        <v>0.03709691372655844</v>
       </c>
       <c r="W96">
-        <v>0.2269594897405464</v>
+        <v>0.2270525477432775</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1499662469797043</v>
+        <v>0.1483876549062337</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9324,22 +9324,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.268310923691098</v>
+        <v>0.270210923691098</v>
       </c>
       <c r="C97">
-        <v>-382.1864054974668</v>
+        <v>-388.6041600572339</v>
       </c>
       <c r="D97">
-        <v>125.9245945025332</v>
+        <v>124.8584399427661</v>
       </c>
       <c r="E97">
-        <v>501.642</v>
+        <v>506.9936</v>
       </c>
       <c r="F97">
-        <v>508.402</v>
+        <v>513.7536</v>
       </c>
       <c r="G97">
         <v>0.291</v>
@@ -9360,37 +9360,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M97">
-        <v>119.8811916</v>
+        <v>121.14309888</v>
       </c>
       <c r="N97">
-        <v>-102.0923027111111</v>
+        <v>-103.3542099911111</v>
       </c>
       <c r="O97">
-        <v>-25.52307567777778</v>
+        <v>-25.83855249777778</v>
       </c>
       <c r="P97">
-        <v>-76.56922703333333</v>
+        <v>-77.51565749333334</v>
       </c>
       <c r="Q97">
-        <v>-75.46922703333334</v>
+        <v>-76.41565749333334</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.052220066699688</v>
+        <v>1.30382508337461</v>
       </c>
       <c r="T97">
-        <v>9.732851234125095</v>
+        <v>12.16606404265637</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03709691372655844</v>
+        <v>0.03671048754190679</v>
       </c>
       <c r="W97">
-        <v>0.2270525477432775</v>
+        <v>0.2271436670376184</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1483876549062337</v>
+        <v>0.1468419501676271</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9406,22 +9406,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2702109236910979</v>
+        <v>0.272110923691098</v>
       </c>
       <c r="C98">
-        <v>-388.6041600572338</v>
+        <v>-395.0040127532242</v>
       </c>
       <c r="D98">
-        <v>124.8584399427662</v>
+        <v>123.8101872467758</v>
       </c>
       <c r="E98">
-        <v>506.9936</v>
+        <v>512.3452</v>
       </c>
       <c r="F98">
-        <v>513.7536</v>
+        <v>519.1052</v>
       </c>
       <c r="G98">
         <v>0.291</v>
@@ -9442,37 +9442,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M98">
-        <v>121.14309888</v>
+        <v>122.40500616</v>
       </c>
       <c r="N98">
-        <v>-103.3542099911111</v>
+        <v>-104.6161172711111</v>
       </c>
       <c r="O98">
-        <v>-25.83855249777778</v>
+        <v>-26.15402931777778</v>
       </c>
       <c r="P98">
-        <v>-77.51565749333334</v>
+        <v>-78.46208795333334</v>
       </c>
       <c r="Q98">
-        <v>-76.41565749333334</v>
+        <v>-77.36208795333334</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.303825083374607</v>
+        <v>1.723166777832809</v>
       </c>
       <c r="T98">
-        <v>12.16606404265634</v>
+        <v>16.22141872354179</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03671048754190679</v>
+        <v>0.03633202890745415</v>
       </c>
       <c r="W98">
-        <v>0.2271436670376184</v>
+        <v>0.2272329075836223</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1468419501676271</v>
+        <v>0.1453281156298166</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9488,22 +9488,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.272110923691098</v>
+        <v>0.2740109236910979</v>
       </c>
       <c r="C99">
-        <v>-395.0040127532242</v>
+        <v>-401.3864107183877</v>
       </c>
       <c r="D99">
-        <v>123.8101872467758</v>
+        <v>122.7793892816123</v>
       </c>
       <c r="E99">
-        <v>512.3452</v>
+        <v>517.6967999999999</v>
       </c>
       <c r="F99">
-        <v>519.1052</v>
+        <v>524.4567999999999</v>
       </c>
       <c r="G99">
         <v>0.291</v>
@@ -9524,37 +9524,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M99">
-        <v>122.40500616</v>
+        <v>123.66691344</v>
       </c>
       <c r="N99">
-        <v>-104.6161172711111</v>
+        <v>-105.8780245511111</v>
       </c>
       <c r="O99">
-        <v>-26.15402931777778</v>
+        <v>-26.46950613777777</v>
       </c>
       <c r="P99">
-        <v>-78.46208795333334</v>
+        <v>-79.40851841333333</v>
       </c>
       <c r="Q99">
-        <v>-77.36208795333334</v>
+        <v>-78.30851841333333</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.723166777832809</v>
+        <v>2.561850166749213</v>
       </c>
       <c r="T99">
-        <v>16.22141872354179</v>
+        <v>24.33212808531268</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03633202890745415</v>
+        <v>0.03596129391860257</v>
       </c>
       <c r="W99">
-        <v>0.2272329075836223</v>
+        <v>0.2273203268939935</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1453281156298166</v>
+        <v>0.1438451756744104</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9570,22 +9570,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2740109236910979</v>
+        <v>0.2759109236910979</v>
       </c>
       <c r="C100">
-        <v>-401.3864107183877</v>
+        <v>-407.7517863179686</v>
       </c>
       <c r="D100">
-        <v>122.7793892816123</v>
+        <v>121.7656136820314</v>
       </c>
       <c r="E100">
-        <v>517.6967999999999</v>
+        <v>523.0484</v>
       </c>
       <c r="F100">
-        <v>524.4567999999999</v>
+        <v>529.8084</v>
       </c>
       <c r="G100">
         <v>0.291</v>
@@ -9606,37 +9606,37 @@
         <v>17.78888888888889</v>
       </c>
       <c r="M100">
-        <v>123.66691344</v>
+        <v>124.92882072</v>
       </c>
       <c r="N100">
-        <v>-105.8780245511111</v>
+        <v>-107.1399318311111</v>
       </c>
       <c r="O100">
-        <v>-26.46950613777777</v>
+        <v>-26.78498295777778</v>
       </c>
       <c r="P100">
-        <v>-79.40851841333333</v>
+        <v>-80.35494887333334</v>
       </c>
       <c r="Q100">
-        <v>-78.30851841333333</v>
+        <v>-79.25494887333335</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.561850166749213</v>
+        <v>5.077900333498427</v>
       </c>
       <c r="T100">
-        <v>24.33212808531268</v>
+        <v>48.66425617062536</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03596129391860257</v>
+        <v>0.03559804852548538</v>
       </c>
       <c r="W100">
-        <v>0.2273203268939935</v>
+        <v>0.2274059801576905</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9644,91 +9644,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1438451756744104</v>
+        <v>0.1423921941019415</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2759109236910979</v>
-      </c>
-      <c r="C101">
-        <v>-407.7517863179686</v>
-      </c>
-      <c r="D101">
-        <v>121.7656136820314</v>
-      </c>
-      <c r="E101">
-        <v>523.0484</v>
-      </c>
-      <c r="F101">
-        <v>529.8084</v>
-      </c>
-      <c r="G101">
-        <v>0.291</v>
-      </c>
-      <c r="H101">
-        <v>528.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>18.88888888888889</v>
-      </c>
-      <c r="K101">
-        <v>1.1</v>
-      </c>
-      <c r="L101">
-        <v>17.78888888888889</v>
-      </c>
-      <c r="M101">
-        <v>124.92882072</v>
-      </c>
-      <c r="N101">
-        <v>-107.1399318311111</v>
-      </c>
-      <c r="O101">
-        <v>-26.78498295777778</v>
-      </c>
-      <c r="P101">
-        <v>-80.35494887333334</v>
-      </c>
-      <c r="Q101">
-        <v>-79.25494887333335</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.077900333498427</v>
-      </c>
-      <c r="T101">
-        <v>48.66425617062536</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03559804852548538</v>
-      </c>
-      <c r="W101">
-        <v>0.2274059801576905</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1423921941019415</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
